--- a/research/traditional_assets/database/data/south_korea/south_korea_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_beverage_soft.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07854104614555765</v>
+        <v>0.07837844353019376</v>
       </c>
       <c r="C2">
-        <v>1805.811284870725</v>
+        <v>1793.309846165592</v>
       </c>
       <c r="D2">
-        <v>1630.611284870725</v>
+        <v>1638.749846165592</v>
       </c>
       <c r="E2">
-        <v>-1325.6</v>
+        <v>-1304.96</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.64</v>
       </c>
       <c r="G2">
         <v>175.2</v>
@@ -1445,28 +1445,28 @@
         <v>329.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.038192</v>
       </c>
       <c r="N2">
-        <v>329.4</v>
+        <v>328.361808</v>
       </c>
       <c r="O2">
-        <v>82.34999999999999</v>
+        <v>82.090452</v>
       </c>
       <c r="P2">
-        <v>247.05</v>
+        <v>246.271356</v>
       </c>
       <c r="Q2">
-        <v>318.15</v>
+        <v>317.371356</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07854104614555765</v>
+        <v>0.07878908437393309</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6612219901513506</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>317.2823523972444</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07837844353019376</v>
+        <v>0.07821584091482987</v>
       </c>
       <c r="C3">
-        <v>1793.309846165592</v>
+        <v>1780.890055896193</v>
       </c>
       <c r="D3">
-        <v>1638.749846165592</v>
+        <v>1646.970055896193</v>
       </c>
       <c r="E3">
-        <v>-1304.96</v>
+        <v>-1284.32</v>
       </c>
       <c r="F3">
-        <v>20.64</v>
+        <v>41.28</v>
       </c>
       <c r="G3">
         <v>175.2</v>
@@ -1527,28 +1527,28 @@
         <v>329.4</v>
       </c>
       <c r="M3">
-        <v>1.038192</v>
+        <v>2.076384</v>
       </c>
       <c r="N3">
-        <v>328.361808</v>
+        <v>327.323616</v>
       </c>
       <c r="O3">
-        <v>82.090452</v>
+        <v>81.83090399999999</v>
       </c>
       <c r="P3">
-        <v>246.271356</v>
+        <v>245.492712</v>
       </c>
       <c r="Q3">
-        <v>317.371356</v>
+        <v>316.592712</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07878908437393309</v>
+        <v>0.07904218460696925</v>
       </c>
       <c r="T3">
-        <v>0.6612219901513506</v>
+        <v>0.6662950451624858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>317.2823523972444</v>
+        <v>158.6411761986222</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07821584091482987</v>
+        <v>0.07805323829946598</v>
       </c>
       <c r="C4">
-        <v>1780.890055896193</v>
+        <v>1768.553148938455</v>
       </c>
       <c r="D4">
-        <v>1646.970055896193</v>
+        <v>1655.273148938456</v>
       </c>
       <c r="E4">
-        <v>-1284.32</v>
+        <v>-1263.68</v>
       </c>
       <c r="F4">
-        <v>41.28</v>
+        <v>61.91999999999999</v>
       </c>
       <c r="G4">
         <v>175.2</v>
@@ -1609,28 +1609,28 @@
         <v>329.4</v>
       </c>
       <c r="M4">
-        <v>2.076384</v>
+        <v>3.114576</v>
       </c>
       <c r="N4">
-        <v>327.323616</v>
+        <v>326.285424</v>
       </c>
       <c r="O4">
-        <v>81.83090399999999</v>
+        <v>81.57135599999999</v>
       </c>
       <c r="P4">
-        <v>245.492712</v>
+        <v>244.714068</v>
       </c>
       <c r="Q4">
-        <v>316.592712</v>
+        <v>315.814068</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07904218460696925</v>
+        <v>0.07930050340151132</v>
       </c>
       <c r="T4">
-        <v>0.6662950451624858</v>
+        <v>0.6714726992460154</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>158.6411761986222</v>
+        <v>105.7607841324148</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07805323829946598</v>
+        <v>0.07789063568410207</v>
       </c>
       <c r="C5">
-        <v>1768.553148938455</v>
+        <v>1756.300385196676</v>
       </c>
       <c r="D5">
-        <v>1655.273148938456</v>
+        <v>1663.660385196676</v>
       </c>
       <c r="E5">
-        <v>-1263.68</v>
+        <v>-1243.04</v>
       </c>
       <c r="F5">
-        <v>61.91999999999999</v>
+        <v>82.56</v>
       </c>
       <c r="G5">
         <v>175.2</v>
@@ -1691,28 +1691,28 @@
         <v>329.4</v>
       </c>
       <c r="M5">
-        <v>3.114576</v>
+        <v>4.152768</v>
       </c>
       <c r="N5">
-        <v>326.285424</v>
+        <v>325.247232</v>
       </c>
       <c r="O5">
-        <v>81.57135599999999</v>
+        <v>81.311808</v>
       </c>
       <c r="P5">
-        <v>244.714068</v>
+        <v>243.935424</v>
       </c>
       <c r="Q5">
-        <v>315.814068</v>
+        <v>315.035424</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07930050340151132</v>
+        <v>0.07956420383760633</v>
       </c>
       <c r="T5">
-        <v>0.6714726992460154</v>
+        <v>0.6767582211229519</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>105.7607841324148</v>
+        <v>79.32058809931111</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07789063568410207</v>
+        <v>0.07772803306873818</v>
       </c>
       <c r="C6">
-        <v>1756.300385196676</v>
+        <v>1744.133050240836</v>
       </c>
       <c r="D6">
-        <v>1663.660385196676</v>
+        <v>1672.133050240836</v>
       </c>
       <c r="E6">
-        <v>-1243.04</v>
+        <v>-1222.4</v>
       </c>
       <c r="F6">
-        <v>82.56</v>
+        <v>103.2</v>
       </c>
       <c r="G6">
         <v>175.2</v>
@@ -1773,28 +1773,28 @@
         <v>329.4</v>
       </c>
       <c r="M6">
-        <v>4.152768</v>
+        <v>5.19096</v>
       </c>
       <c r="N6">
-        <v>325.247232</v>
+        <v>324.20904</v>
       </c>
       <c r="O6">
-        <v>81.311808</v>
+        <v>81.05225999999999</v>
       </c>
       <c r="P6">
-        <v>243.935424</v>
+        <v>243.15678</v>
       </c>
       <c r="Q6">
-        <v>315.035424</v>
+        <v>314.2567799999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07956420383760633</v>
+        <v>0.07983345586182966</v>
       </c>
       <c r="T6">
-        <v>0.6767582211229519</v>
+        <v>0.6821550171446661</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>79.32058809931111</v>
+        <v>63.45647047944888</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07772803306873818</v>
+        <v>0.07756543045337429</v>
       </c>
       <c r="C7">
-        <v>1744.133050240836</v>
+        <v>1732.052455963502</v>
       </c>
       <c r="D7">
-        <v>1672.133050240836</v>
+        <v>1680.692455963502</v>
       </c>
       <c r="E7">
-        <v>-1222.4</v>
+        <v>-1201.76</v>
       </c>
       <c r="F7">
-        <v>103.2</v>
+        <v>123.84</v>
       </c>
       <c r="G7">
         <v>175.2</v>
@@ -1855,28 +1855,28 @@
         <v>329.4</v>
       </c>
       <c r="M7">
-        <v>5.19096</v>
+        <v>6.229152</v>
       </c>
       <c r="N7">
-        <v>324.20904</v>
+        <v>323.170848</v>
       </c>
       <c r="O7">
-        <v>81.05225999999999</v>
+        <v>80.79271199999999</v>
       </c>
       <c r="P7">
-        <v>243.15678</v>
+        <v>242.378136</v>
       </c>
       <c r="Q7">
-        <v>314.2567799999999</v>
+        <v>313.4781359999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07983345586182966</v>
+        <v>0.08010843665252584</v>
       </c>
       <c r="T7">
-        <v>0.6821550171446661</v>
+        <v>0.6876666386136507</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.45647047944888</v>
+        <v>52.88039206620741</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07756543045337429</v>
+        <v>0.0774028278380104</v>
       </c>
       <c r="C8">
-        <v>1732.052455963502</v>
+        <v>1720.059941256996</v>
       </c>
       <c r="D8">
-        <v>1680.692455963502</v>
+        <v>1689.339941256996</v>
       </c>
       <c r="E8">
-        <v>-1201.76</v>
+        <v>-1181.12</v>
       </c>
       <c r="F8">
-        <v>123.84</v>
+        <v>144.48</v>
       </c>
       <c r="G8">
         <v>175.2</v>
@@ -1937,28 +1937,28 @@
         <v>329.4</v>
       </c>
       <c r="M8">
-        <v>6.229151999999999</v>
+        <v>7.267343999999999</v>
       </c>
       <c r="N8">
-        <v>323.170848</v>
+        <v>322.132656</v>
       </c>
       <c r="O8">
-        <v>80.79271199999999</v>
+        <v>80.533164</v>
       </c>
       <c r="P8">
-        <v>242.378136</v>
+        <v>241.599492</v>
       </c>
       <c r="Q8">
-        <v>313.4781359999999</v>
+        <v>312.699492</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08010843665252584</v>
+        <v>0.08038933100861334</v>
       </c>
       <c r="T8">
-        <v>0.6876666386136507</v>
+        <v>0.693296789576592</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.88039206620741</v>
+        <v>45.3260503424635</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0774028278380104</v>
+        <v>0.07724022522264651</v>
       </c>
       <c r="C9">
-        <v>1720.059941256996</v>
+        <v>1708.156872711584</v>
       </c>
       <c r="D9">
-        <v>1689.339941256996</v>
+        <v>1698.076872711584</v>
       </c>
       <c r="E9">
-        <v>-1181.12</v>
+        <v>-1160.48</v>
       </c>
       <c r="F9">
-        <v>144.48</v>
+        <v>165.12</v>
       </c>
       <c r="G9">
         <v>175.2</v>
@@ -2019,28 +2019,28 @@
         <v>329.4</v>
       </c>
       <c r="M9">
-        <v>7.267344</v>
+        <v>8.305536</v>
       </c>
       <c r="N9">
-        <v>322.132656</v>
+        <v>321.094464</v>
       </c>
       <c r="O9">
-        <v>80.533164</v>
+        <v>80.27361599999999</v>
       </c>
       <c r="P9">
-        <v>241.599492</v>
+        <v>240.820848</v>
       </c>
       <c r="Q9">
-        <v>312.699492</v>
+        <v>311.920848</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08038933100861334</v>
+        <v>0.0806763317637462</v>
       </c>
       <c r="T9">
-        <v>0.693296789576592</v>
+        <v>0.6990493351256842</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.32605034246349</v>
+        <v>39.66029404965555</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07724022522264651</v>
+        <v>0.07707762260728261</v>
       </c>
       <c r="C10">
-        <v>1708.156872711584</v>
+        <v>1696.344645335439</v>
       </c>
       <c r="D10">
-        <v>1698.076872711584</v>
+        <v>1706.904645335439</v>
       </c>
       <c r="E10">
-        <v>-1160.48</v>
+        <v>-1139.84</v>
       </c>
       <c r="F10">
-        <v>165.12</v>
+        <v>185.76</v>
       </c>
       <c r="G10">
         <v>175.2</v>
@@ -2101,28 +2101,28 @@
         <v>329.4</v>
       </c>
       <c r="M10">
-        <v>8.305536</v>
+        <v>9.343727999999999</v>
       </c>
       <c r="N10">
-        <v>321.094464</v>
+        <v>320.056272</v>
       </c>
       <c r="O10">
-        <v>80.27361599999999</v>
+        <v>80.01406799999999</v>
       </c>
       <c r="P10">
-        <v>240.820848</v>
+        <v>240.042204</v>
       </c>
       <c r="Q10">
-        <v>311.920848</v>
+        <v>311.142204</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0806763317637462</v>
+        <v>0.08096964022778308</v>
       </c>
       <c r="T10">
-        <v>0.6990493351256842</v>
+        <v>0.7049283102472839</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.66029404965555</v>
+        <v>35.25359471080494</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07707762260728261</v>
+        <v>0.07691501999191871</v>
       </c>
       <c r="C11">
-        <v>1696.344645335439</v>
+        <v>1684.624683297183</v>
       </c>
       <c r="D11">
-        <v>1706.904645335439</v>
+        <v>1715.824683297183</v>
       </c>
       <c r="E11">
-        <v>-1139.84</v>
+        <v>-1119.2</v>
       </c>
       <c r="F11">
-        <v>185.76</v>
+        <v>206.4</v>
       </c>
       <c r="G11">
         <v>175.2</v>
@@ -2183,28 +2183,28 @@
         <v>329.4</v>
       </c>
       <c r="M11">
-        <v>9.343727999999999</v>
+        <v>10.38192</v>
       </c>
       <c r="N11">
-        <v>320.056272</v>
+        <v>319.01808</v>
       </c>
       <c r="O11">
-        <v>80.01406799999999</v>
+        <v>79.75452</v>
       </c>
       <c r="P11">
-        <v>240.042204</v>
+        <v>239.26356</v>
       </c>
       <c r="Q11">
-        <v>311.142204</v>
+        <v>310.36356</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08096964022778308</v>
+        <v>0.08126946665768746</v>
       </c>
       <c r="T11">
-        <v>0.7049283102472839</v>
+        <v>0.7109379292604747</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.25359471080494</v>
+        <v>31.72823523972445</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07691501999191871</v>
+        <v>0.07675241737655482</v>
       </c>
       <c r="C12">
-        <v>1684.624683297183</v>
+        <v>1672.998440691828</v>
       </c>
       <c r="D12">
-        <v>1715.824683297183</v>
+        <v>1724.838440691828</v>
       </c>
       <c r="E12">
-        <v>-1119.2</v>
+        <v>-1098.56</v>
       </c>
       <c r="F12">
-        <v>206.4</v>
+        <v>227.04</v>
       </c>
       <c r="G12">
         <v>175.2</v>
@@ -2265,28 +2265,28 @@
         <v>329.4</v>
       </c>
       <c r="M12">
-        <v>10.38192</v>
+        <v>11.420112</v>
       </c>
       <c r="N12">
-        <v>319.01808</v>
+        <v>317.979888</v>
       </c>
       <c r="O12">
-        <v>79.75452</v>
+        <v>79.49497199999999</v>
       </c>
       <c r="P12">
-        <v>239.26356</v>
+        <v>238.484916</v>
       </c>
       <c r="Q12">
-        <v>310.36356</v>
+        <v>309.584916</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08126946665768746</v>
+        <v>0.08157603076017396</v>
       </c>
       <c r="T12">
-        <v>0.7109379292604747</v>
+        <v>0.7170825958919396</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.72823523972445</v>
+        <v>28.84385021793131</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07675241737655482</v>
+        <v>0.07658981476119094</v>
       </c>
       <c r="C13">
-        <v>1672.998440691828</v>
+        <v>1661.467402330992</v>
       </c>
       <c r="D13">
-        <v>1724.838440691828</v>
+        <v>1733.947402330992</v>
       </c>
       <c r="E13">
-        <v>-1098.56</v>
+        <v>-1077.92</v>
       </c>
       <c r="F13">
-        <v>227.04</v>
+        <v>247.68</v>
       </c>
       <c r="G13">
         <v>175.2</v>
@@ -2347,28 +2347,28 @@
         <v>329.4</v>
       </c>
       <c r="M13">
-        <v>11.420112</v>
+        <v>12.458304</v>
       </c>
       <c r="N13">
-        <v>317.979888</v>
+        <v>316.941696</v>
       </c>
       <c r="O13">
-        <v>79.49497199999999</v>
+        <v>79.23542399999999</v>
       </c>
       <c r="P13">
-        <v>238.484916</v>
+        <v>237.706272</v>
       </c>
       <c r="Q13">
-        <v>309.584916</v>
+        <v>308.806272</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08157603076017396</v>
+        <v>0.08188956222862606</v>
       </c>
       <c r="T13">
-        <v>0.7170825958919396</v>
+        <v>0.7233669140377558</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.84385021793131</v>
+        <v>26.44019603310371</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07658981476119094</v>
+        <v>0.07642721214582704</v>
       </c>
       <c r="C14">
-        <v>1661.467402330992</v>
+        <v>1650.033084558288</v>
       </c>
       <c r="D14">
-        <v>1733.947402330992</v>
+        <v>1743.153084558287</v>
       </c>
       <c r="E14">
-        <v>-1077.92</v>
+        <v>-1057.28</v>
       </c>
       <c r="F14">
-        <v>247.68</v>
+        <v>268.32</v>
       </c>
       <c r="G14">
         <v>175.2</v>
@@ -2429,28 +2429,28 @@
         <v>329.4</v>
       </c>
       <c r="M14">
-        <v>12.458304</v>
+        <v>13.496496</v>
       </c>
       <c r="N14">
-        <v>316.941696</v>
+        <v>315.903504</v>
       </c>
       <c r="O14">
-        <v>79.23542399999999</v>
+        <v>78.975876</v>
       </c>
       <c r="P14">
-        <v>237.706272</v>
+        <v>236.927628</v>
       </c>
       <c r="Q14">
-        <v>308.806272</v>
+        <v>308.027628</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08188956222862606</v>
+        <v>0.08221030131704257</v>
       </c>
       <c r="T14">
-        <v>0.7233669140377558</v>
+        <v>0.7297956992673839</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.44019603310371</v>
+        <v>24.40633479978803</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07642721214582704</v>
+        <v>0.07626460953046313</v>
       </c>
       <c r="C15">
-        <v>1650.033084558288</v>
+        <v>1638.697036090816</v>
       </c>
       <c r="D15">
-        <v>1743.153084558287</v>
+        <v>1752.457036090816</v>
       </c>
       <c r="E15">
-        <v>-1057.28</v>
+        <v>-1036.64</v>
       </c>
       <c r="F15">
-        <v>268.32</v>
+        <v>288.96</v>
       </c>
       <c r="G15">
         <v>175.2</v>
@@ -2511,28 +2511,28 @@
         <v>329.4</v>
       </c>
       <c r="M15">
-        <v>13.496496</v>
+        <v>14.534688</v>
       </c>
       <c r="N15">
-        <v>315.903504</v>
+        <v>314.865312</v>
       </c>
       <c r="O15">
-        <v>78.975876</v>
+        <v>78.71632799999999</v>
       </c>
       <c r="P15">
-        <v>236.927628</v>
+        <v>236.148984</v>
       </c>
       <c r="Q15">
-        <v>308.027628</v>
+        <v>307.248984</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08221030131704257</v>
+        <v>0.0825384994540269</v>
       </c>
       <c r="T15">
-        <v>0.7297956992673839</v>
+        <v>0.7363739911302591</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.40633479978803</v>
+        <v>22.66302517123174</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07626460953046313</v>
+        <v>0.07610200691509925</v>
       </c>
       <c r="C16">
-        <v>1638.697036090816</v>
+        <v>1627.46083888776</v>
       </c>
       <c r="D16">
-        <v>1752.457036090816</v>
+        <v>1761.860838887759</v>
       </c>
       <c r="E16">
-        <v>-1036.64</v>
+        <v>-1016</v>
       </c>
       <c r="F16">
-        <v>288.96</v>
+        <v>309.6</v>
       </c>
       <c r="G16">
         <v>175.2</v>
@@ -2593,28 +2593,28 @@
         <v>329.4</v>
       </c>
       <c r="M16">
-        <v>14.534688</v>
+        <v>15.57288</v>
       </c>
       <c r="N16">
-        <v>314.865312</v>
+        <v>313.82712</v>
       </c>
       <c r="O16">
-        <v>78.71632799999999</v>
+        <v>78.45677999999999</v>
       </c>
       <c r="P16">
-        <v>236.148984</v>
+        <v>235.37034</v>
       </c>
       <c r="Q16">
-        <v>307.248984</v>
+        <v>306.47034</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0825384994540269</v>
+        <v>0.08287441990011676</v>
       </c>
       <c r="T16">
-        <v>0.7363739911302591</v>
+        <v>0.7431070663310845</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.66302517123174</v>
+        <v>21.15215682648296</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07610200691509925</v>
+        <v>0.07593940429973534</v>
       </c>
       <c r="C17">
-        <v>1627.46083888776</v>
+        <v>1616.326109047094</v>
       </c>
       <c r="D17">
-        <v>1761.860838887759</v>
+        <v>1771.366109047094</v>
       </c>
       <c r="E17">
-        <v>-1016</v>
+        <v>-995.3599999999999</v>
       </c>
       <c r="F17">
-        <v>309.6</v>
+        <v>330.24</v>
       </c>
       <c r="G17">
         <v>175.2</v>
@@ -2675,28 +2675,28 @@
         <v>329.4</v>
       </c>
       <c r="M17">
-        <v>15.57288</v>
+        <v>16.611072</v>
       </c>
       <c r="N17">
-        <v>313.82712</v>
+        <v>312.788928</v>
       </c>
       <c r="O17">
-        <v>78.45677999999999</v>
+        <v>78.197232</v>
       </c>
       <c r="P17">
-        <v>235.37034</v>
+        <v>234.591696</v>
       </c>
       <c r="Q17">
-        <v>306.47034</v>
+        <v>305.691696</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08287441990011676</v>
+        <v>0.08321833845206589</v>
       </c>
       <c r="T17">
-        <v>0.7431070663310845</v>
+        <v>0.7500004528462151</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.15215682648297</v>
+        <v>19.83014702482778</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07593940429973534</v>
+        <v>0.07577680168437145</v>
       </c>
       <c r="C18">
-        <v>1616.326109047094</v>
+        <v>1605.294497731474</v>
       </c>
       <c r="D18">
-        <v>1771.366109047094</v>
+        <v>1780.974497731474</v>
       </c>
       <c r="E18">
-        <v>-995.3599999999999</v>
+        <v>-974.7199999999998</v>
       </c>
       <c r="F18">
-        <v>330.24</v>
+        <v>350.8800000000001</v>
       </c>
       <c r="G18">
         <v>175.2</v>
@@ -2757,28 +2757,28 @@
         <v>329.4</v>
       </c>
       <c r="M18">
-        <v>16.611072</v>
+        <v>17.649264</v>
       </c>
       <c r="N18">
-        <v>312.788928</v>
+        <v>311.750736</v>
       </c>
       <c r="O18">
-        <v>78.197232</v>
+        <v>77.93768399999999</v>
       </c>
       <c r="P18">
-        <v>234.591696</v>
+        <v>233.813052</v>
       </c>
       <c r="Q18">
-        <v>305.691696</v>
+        <v>304.913052</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08321833845206589</v>
+        <v>0.0835705441980379</v>
       </c>
       <c r="T18">
-        <v>0.7500004528462151</v>
+        <v>0.7570599450605057</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.83014702482778</v>
+        <v>18.6636677880732</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07577680168437145</v>
+        <v>0.07561419906900757</v>
       </c>
       <c r="C19">
-        <v>1605.294497731474</v>
+        <v>1594.367692124428</v>
       </c>
       <c r="D19">
-        <v>1780.974497731474</v>
+        <v>1790.687692124428</v>
       </c>
       <c r="E19">
-        <v>-974.7199999999998</v>
+        <v>-954.0799999999999</v>
       </c>
       <c r="F19">
-        <v>350.8800000000001</v>
+        <v>371.52</v>
       </c>
       <c r="G19">
         <v>175.2</v>
@@ -2839,28 +2839,28 @@
         <v>329.4</v>
       </c>
       <c r="M19">
-        <v>17.649264</v>
+        <v>18.687456</v>
       </c>
       <c r="N19">
-        <v>311.750736</v>
+        <v>310.712544</v>
       </c>
       <c r="O19">
-        <v>77.93768399999999</v>
+        <v>77.67813599999999</v>
       </c>
       <c r="P19">
-        <v>233.813052</v>
+        <v>233.034408</v>
       </c>
       <c r="Q19">
-        <v>304.913052</v>
+        <v>304.134408</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0835705441980379</v>
+        <v>0.083931340328058</v>
       </c>
       <c r="T19">
-        <v>0.7570599450605057</v>
+        <v>0.7642916200117299</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.6636677880732</v>
+        <v>17.62679735540247</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07561419906900757</v>
+        <v>0.07545159645364367</v>
       </c>
       <c r="C20">
-        <v>1594.367692124428</v>
+        <v>1583.547416418012</v>
       </c>
       <c r="D20">
-        <v>1790.687692124428</v>
+        <v>1800.507416418012</v>
       </c>
       <c r="E20">
-        <v>-954.0799999999999</v>
+        <v>-933.4399999999998</v>
       </c>
       <c r="F20">
-        <v>371.52</v>
+        <v>392.16</v>
       </c>
       <c r="G20">
         <v>175.2</v>
@@ -2921,28 +2921,28 @@
         <v>329.4</v>
       </c>
       <c r="M20">
-        <v>18.687456</v>
+        <v>19.725648</v>
       </c>
       <c r="N20">
-        <v>310.712544</v>
+        <v>309.674352</v>
       </c>
       <c r="O20">
-        <v>77.67813599999999</v>
+        <v>77.418588</v>
       </c>
       <c r="P20">
-        <v>233.034408</v>
+        <v>232.255764</v>
       </c>
       <c r="Q20">
-        <v>304.134408</v>
+        <v>303.355764</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.083931340328058</v>
+        <v>0.08430104500449837</v>
       </c>
       <c r="T20">
-        <v>0.7642916200117299</v>
+        <v>0.7717018548382932</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.62679735540247</v>
+        <v>16.69907117880234</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07545159645364367</v>
+        <v>0.07528899383827978</v>
       </c>
       <c r="C21">
-        <v>1583.547416418012</v>
+        <v>1572.835432833127</v>
       </c>
       <c r="D21">
-        <v>1800.507416418012</v>
+        <v>1810.435432833126</v>
       </c>
       <c r="E21">
-        <v>-933.4399999999998</v>
+        <v>-912.8</v>
       </c>
       <c r="F21">
-        <v>392.16</v>
+        <v>412.8</v>
       </c>
       <c r="G21">
         <v>175.2</v>
@@ -3003,28 +3003,28 @@
         <v>329.4</v>
       </c>
       <c r="M21">
-        <v>19.725648</v>
+        <v>20.76384</v>
       </c>
       <c r="N21">
-        <v>309.674352</v>
+        <v>308.63616</v>
       </c>
       <c r="O21">
-        <v>77.418588</v>
+        <v>77.15903999999999</v>
       </c>
       <c r="P21">
-        <v>232.255764</v>
+        <v>231.47712</v>
       </c>
       <c r="Q21">
-        <v>303.355764</v>
+        <v>302.5771199999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08430104500449837</v>
+        <v>0.08467999229784973</v>
       </c>
       <c r="T21">
-        <v>0.7717018548382932</v>
+        <v>0.7792973455355204</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.69907117880234</v>
+        <v>15.86411761986222</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07528899383827978</v>
+        <v>0.07512639122291588</v>
       </c>
       <c r="C22">
-        <v>1572.835432833127</v>
+        <v>1562.233542673798</v>
       </c>
       <c r="D22">
-        <v>1810.435432833126</v>
+        <v>1820.473542673798</v>
       </c>
       <c r="E22">
-        <v>-912.8</v>
+        <v>-892.1599999999999</v>
       </c>
       <c r="F22">
-        <v>412.8</v>
+        <v>433.4400000000001</v>
       </c>
       <c r="G22">
         <v>175.2</v>
@@ -3085,28 +3085,28 @@
         <v>329.4</v>
       </c>
       <c r="M22">
-        <v>20.76384</v>
+        <v>21.802032</v>
       </c>
       <c r="N22">
-        <v>308.63616</v>
+        <v>307.597968</v>
       </c>
       <c r="O22">
-        <v>77.15903999999999</v>
+        <v>76.899492</v>
       </c>
       <c r="P22">
-        <v>231.47712</v>
+        <v>230.698476</v>
       </c>
       <c r="Q22">
-        <v>302.5771199999999</v>
+        <v>301.7984759999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08467999229784973</v>
+        <v>0.0850685331935644</v>
       </c>
       <c r="T22">
-        <v>0.7792973455355204</v>
+        <v>0.7870851271364749</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.86411761986222</v>
+        <v>15.10868344748783</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07512639122291587</v>
+        <v>0.07496378860755198</v>
       </c>
       <c r="C23">
-        <v>1562.233542673799</v>
+        <v>1551.743587416712</v>
       </c>
       <c r="D23">
-        <v>1820.473542673799</v>
+        <v>1830.623587416712</v>
       </c>
       <c r="E23">
-        <v>-892.1599999999999</v>
+        <v>-871.52</v>
       </c>
       <c r="F23">
-        <v>433.44</v>
+        <v>454.08</v>
       </c>
       <c r="G23">
         <v>175.2</v>
@@ -3167,28 +3167,28 @@
         <v>329.4</v>
       </c>
       <c r="M23">
-        <v>21.802032</v>
+        <v>22.840224</v>
       </c>
       <c r="N23">
-        <v>307.597968</v>
+        <v>306.559776</v>
       </c>
       <c r="O23">
-        <v>76.899492</v>
+        <v>76.639944</v>
       </c>
       <c r="P23">
-        <v>230.698476</v>
+        <v>229.919832</v>
       </c>
       <c r="Q23">
-        <v>301.7984759999999</v>
+        <v>301.019832</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0850685331935644</v>
+        <v>0.0854670366763487</v>
       </c>
       <c r="T23">
-        <v>0.7870851271364749</v>
+        <v>0.7950725954451463</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.10868344748783</v>
+        <v>14.42192510896566</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07496378860755198</v>
+        <v>0.07480118599218809</v>
       </c>
       <c r="C24">
-        <v>1551.743587416712</v>
+        <v>1541.367449837407</v>
       </c>
       <c r="D24">
-        <v>1830.623587416712</v>
+        <v>1840.887449837407</v>
       </c>
       <c r="E24">
-        <v>-871.52</v>
+        <v>-850.8799999999999</v>
       </c>
       <c r="F24">
-        <v>454.08</v>
+        <v>474.72</v>
       </c>
       <c r="G24">
         <v>175.2</v>
@@ -3249,28 +3249,28 @@
         <v>329.4</v>
       </c>
       <c r="M24">
-        <v>22.840224</v>
+        <v>23.878416</v>
       </c>
       <c r="N24">
-        <v>306.559776</v>
+        <v>305.521584</v>
       </c>
       <c r="O24">
-        <v>76.639944</v>
+        <v>76.38039599999999</v>
       </c>
       <c r="P24">
-        <v>229.919832</v>
+        <v>229.141188</v>
       </c>
       <c r="Q24">
-        <v>301.019832</v>
+        <v>300.241188</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0854670366763487</v>
+        <v>0.08587589089894557</v>
       </c>
       <c r="T24">
-        <v>0.7950725954451463</v>
+        <v>0.8032675304631338</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.42192510896566</v>
+        <v>13.79488488683671</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07480118599218809</v>
+        <v>0.07463858337682419</v>
       </c>
       <c r="C25">
-        <v>1541.367449837407</v>
+        <v>1531.107055174564</v>
       </c>
       <c r="D25">
-        <v>1840.887449837407</v>
+        <v>1851.267055174564</v>
       </c>
       <c r="E25">
-        <v>-850.8799999999999</v>
+        <v>-830.2399999999999</v>
       </c>
       <c r="F25">
-        <v>474.72</v>
+        <v>495.36</v>
       </c>
       <c r="G25">
         <v>175.2</v>
@@ -3331,28 +3331,28 @@
         <v>329.4</v>
       </c>
       <c r="M25">
-        <v>23.878416</v>
+        <v>24.916608</v>
       </c>
       <c r="N25">
-        <v>305.521584</v>
+        <v>304.483392</v>
       </c>
       <c r="O25">
-        <v>76.38039599999999</v>
+        <v>76.120848</v>
       </c>
       <c r="P25">
-        <v>229.141188</v>
+        <v>228.362544</v>
       </c>
       <c r="Q25">
-        <v>300.241188</v>
+        <v>299.462544</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08587589089894557</v>
+        <v>0.08629550444318973</v>
       </c>
       <c r="T25">
-        <v>0.8032675304631338</v>
+        <v>0.8116781216658052</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.79488488683671</v>
+        <v>13.22009801655185</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07463858337682419</v>
+        <v>0.07475723076146031</v>
       </c>
       <c r="C26">
-        <v>1531.107055174564</v>
+        <v>1502.881799658633</v>
       </c>
       <c r="D26">
-        <v>1851.267055174564</v>
+        <v>1843.681799658633</v>
       </c>
       <c r="E26">
-        <v>-830.24</v>
+        <v>-809.5999999999999</v>
       </c>
       <c r="F26">
-        <v>495.36</v>
+        <v>516</v>
       </c>
       <c r="G26">
         <v>175.2</v>
@@ -3413,45 +3413,45 @@
         <v>329.4</v>
       </c>
       <c r="M26">
-        <v>24.916608</v>
+        <v>26.7288</v>
       </c>
       <c r="N26">
-        <v>304.483392</v>
+        <v>302.6712</v>
       </c>
       <c r="O26">
-        <v>76.120848</v>
+        <v>75.6678</v>
       </c>
       <c r="P26">
-        <v>228.362544</v>
+        <v>227.0034</v>
       </c>
       <c r="Q26">
-        <v>299.462544</v>
+        <v>298.1034</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08629550444318973</v>
+        <v>0.08672630768194707</v>
       </c>
       <c r="T26">
-        <v>0.8116781216658052</v>
+        <v>0.8203129953005478</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.22009801655185</v>
+        <v>12.32378557959953</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07475723076146031</v>
+        <v>0.0746058781460964</v>
       </c>
       <c r="C27">
-        <v>1502.881799658633</v>
+        <v>1491.928921879379</v>
       </c>
       <c r="D27">
-        <v>1843.681799658633</v>
+        <v>1853.368921879379</v>
       </c>
       <c r="E27">
-        <v>-809.5999999999999</v>
+        <v>-788.9599999999999</v>
       </c>
       <c r="F27">
-        <v>516</v>
+        <v>536.64</v>
       </c>
       <c r="G27">
         <v>175.2</v>
@@ -3495,28 +3495,28 @@
         <v>329.4</v>
       </c>
       <c r="M27">
-        <v>26.7288</v>
+        <v>27.797952</v>
       </c>
       <c r="N27">
-        <v>302.6712</v>
+        <v>301.602048</v>
       </c>
       <c r="O27">
-        <v>75.6678</v>
+        <v>75.40051199999999</v>
       </c>
       <c r="P27">
-        <v>227.0034</v>
+        <v>226.201536</v>
       </c>
       <c r="Q27">
-        <v>298.1034</v>
+        <v>297.3015359999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08672630768194707</v>
+        <v>0.08716875425148163</v>
       </c>
       <c r="T27">
-        <v>0.8203129953005478</v>
+        <v>0.8291812438983917</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.32378557959953</v>
+        <v>11.84979382653801</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0746058781460964</v>
+        <v>0.07445452553073251</v>
       </c>
       <c r="C28">
-        <v>1491.928921879379</v>
+        <v>1481.078378461368</v>
       </c>
       <c r="D28">
-        <v>1853.368921879379</v>
+        <v>1863.158378461368</v>
       </c>
       <c r="E28">
-        <v>-788.9599999999999</v>
+        <v>-768.3199999999998</v>
       </c>
       <c r="F28">
-        <v>536.64</v>
+        <v>557.2800000000001</v>
       </c>
       <c r="G28">
         <v>175.2</v>
@@ -3577,28 +3577,28 @@
         <v>329.4</v>
       </c>
       <c r="M28">
-        <v>27.797952</v>
+        <v>28.867104</v>
       </c>
       <c r="N28">
-        <v>301.602048</v>
+        <v>300.532896</v>
       </c>
       <c r="O28">
-        <v>75.40051199999999</v>
+        <v>75.133224</v>
       </c>
       <c r="P28">
-        <v>226.201536</v>
+        <v>225.399672</v>
       </c>
       <c r="Q28">
-        <v>297.3015359999999</v>
+        <v>296.499672</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08716875425148163</v>
+        <v>0.08762332264483906</v>
       </c>
       <c r="T28">
-        <v>0.8291812438983917</v>
+        <v>0.8382924582112448</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.84979382653801</v>
+        <v>11.41091257370327</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07445452553073251</v>
+        <v>0.07430317291536863</v>
       </c>
       <c r="C29">
-        <v>1481.078378461368</v>
+        <v>1470.331799599237</v>
       </c>
       <c r="D29">
-        <v>1863.158378461368</v>
+        <v>1873.051799599237</v>
       </c>
       <c r="E29">
-        <v>-768.3199999999998</v>
+        <v>-747.6799999999998</v>
       </c>
       <c r="F29">
-        <v>557.2800000000001</v>
+        <v>577.9200000000001</v>
       </c>
       <c r="G29">
         <v>175.2</v>
@@ -3659,28 +3659,28 @@
         <v>329.4</v>
       </c>
       <c r="M29">
-        <v>28.867104</v>
+        <v>29.936256</v>
       </c>
       <c r="N29">
-        <v>300.532896</v>
+        <v>299.463744</v>
       </c>
       <c r="O29">
-        <v>75.133224</v>
+        <v>74.86593599999999</v>
       </c>
       <c r="P29">
-        <v>225.399672</v>
+        <v>224.597808</v>
       </c>
       <c r="Q29">
-        <v>296.499672</v>
+        <v>295.697808</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08762332264483906</v>
+        <v>0.08809051793801198</v>
       </c>
       <c r="T29">
-        <v>0.8382924582112448</v>
+        <v>0.8476567618105662</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.41091257370327</v>
+        <v>11.0033799817853</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07430317291536863</v>
+        <v>0.07415182030000472</v>
       </c>
       <c r="C30">
-        <v>1470.331799599237</v>
+        <v>1459.690850297981</v>
       </c>
       <c r="D30">
-        <v>1873.051799599237</v>
+        <v>1883.050850297981</v>
       </c>
       <c r="E30">
-        <v>-747.6799999999998</v>
+        <v>-727.0399999999998</v>
       </c>
       <c r="F30">
-        <v>577.9200000000001</v>
+        <v>598.5600000000001</v>
       </c>
       <c r="G30">
         <v>175.2</v>
@@ -3741,28 +3741,28 @@
         <v>329.4</v>
       </c>
       <c r="M30">
-        <v>29.936256</v>
+        <v>31.005408</v>
       </c>
       <c r="N30">
-        <v>299.463744</v>
+        <v>298.394592</v>
       </c>
       <c r="O30">
-        <v>74.86593599999999</v>
+        <v>74.598648</v>
       </c>
       <c r="P30">
-        <v>224.597808</v>
+        <v>223.795944</v>
       </c>
       <c r="Q30">
-        <v>295.697808</v>
+        <v>294.895944</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08809051793801198</v>
+        <v>0.08857087366197849</v>
       </c>
       <c r="T30">
-        <v>0.8476567618105662</v>
+        <v>0.8572848486098682</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.0033799817853</v>
+        <v>10.62395308586166</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07415182030000472</v>
+        <v>0.07400046768464083</v>
       </c>
       <c r="C31">
-        <v>1459.690850297981</v>
+        <v>1449.157231307081</v>
       </c>
       <c r="D31">
-        <v>1883.050850297981</v>
+        <v>1893.157231307081</v>
       </c>
       <c r="E31">
-        <v>-727.04</v>
+        <v>-706.4</v>
       </c>
       <c r="F31">
-        <v>598.5599999999999</v>
+        <v>619.1999999999999</v>
       </c>
       <c r="G31">
         <v>175.2</v>
@@ -3823,28 +3823,28 @@
         <v>329.4</v>
       </c>
       <c r="M31">
-        <v>31.005408</v>
+        <v>32.07456</v>
       </c>
       <c r="N31">
-        <v>298.394592</v>
+        <v>297.32544</v>
       </c>
       <c r="O31">
-        <v>74.598648</v>
+        <v>74.33135999999999</v>
       </c>
       <c r="P31">
-        <v>223.795944</v>
+        <v>222.99408</v>
       </c>
       <c r="Q31">
-        <v>294.895944</v>
+        <v>294.09408</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08857087366197849</v>
+        <v>0.08906495383520119</v>
       </c>
       <c r="T31">
-        <v>0.8572848486098682</v>
+        <v>0.8671880236034363</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.62395308586167</v>
+        <v>10.26982131633294</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07400046768464083</v>
+        <v>0.07384911506927694</v>
       </c>
       <c r="C32">
-        <v>1449.157231307081</v>
+        <v>1438.732680084901</v>
       </c>
       <c r="D32">
-        <v>1893.157231307081</v>
+        <v>1903.372680084902</v>
       </c>
       <c r="E32">
-        <v>-706.4</v>
+        <v>-685.7599999999999</v>
       </c>
       <c r="F32">
-        <v>619.1999999999999</v>
+        <v>639.84</v>
       </c>
       <c r="G32">
         <v>175.2</v>
@@ -3905,28 +3905,28 @@
         <v>329.4</v>
       </c>
       <c r="M32">
-        <v>32.07456</v>
+        <v>33.143712</v>
       </c>
       <c r="N32">
-        <v>297.32544</v>
+        <v>296.256288</v>
       </c>
       <c r="O32">
-        <v>74.33135999999999</v>
+        <v>74.064072</v>
       </c>
       <c r="P32">
-        <v>222.99408</v>
+        <v>222.192216</v>
       </c>
       <c r="Q32">
-        <v>294.09408</v>
+        <v>293.2922159999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08906495383520119</v>
+        <v>0.08957335517286513</v>
       </c>
       <c r="T32">
-        <v>0.8671880236034363</v>
+        <v>0.8773782471475424</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.26982131633294</v>
+        <v>9.938536757741558</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07384911506927694</v>
+        <v>0.07410576245391304</v>
       </c>
       <c r="C33">
-        <v>1438.732680084901</v>
+        <v>1400.834864785739</v>
       </c>
       <c r="D33">
-        <v>1903.372680084902</v>
+        <v>1886.114864785739</v>
       </c>
       <c r="E33">
-        <v>-685.7599999999999</v>
+        <v>-665.1199999999999</v>
       </c>
       <c r="F33">
-        <v>639.84</v>
+        <v>660.48</v>
       </c>
       <c r="G33">
         <v>175.2</v>
@@ -3987,45 +3987,45 @@
         <v>329.4</v>
       </c>
       <c r="M33">
-        <v>33.143712</v>
+        <v>35.33568</v>
       </c>
       <c r="N33">
-        <v>296.256288</v>
+        <v>294.06432</v>
       </c>
       <c r="O33">
-        <v>74.064072</v>
+        <v>73.51607999999999</v>
       </c>
       <c r="P33">
-        <v>222.192216</v>
+        <v>220.54824</v>
       </c>
       <c r="Q33">
-        <v>293.2922159999999</v>
+        <v>291.64824</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08957335517286513</v>
+        <v>0.09009670949104859</v>
       </c>
       <c r="T33">
-        <v>0.8773782471475424</v>
+        <v>0.8878681831488282</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.938536757741558</v>
+        <v>9.322022386437729</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07410576245391304</v>
+        <v>0.07396715983854914</v>
       </c>
       <c r="C34">
-        <v>1400.834864785739</v>
+        <v>1389.47590180312</v>
       </c>
       <c r="D34">
-        <v>1886.114864785739</v>
+        <v>1895.395901803119</v>
       </c>
       <c r="E34">
-        <v>-665.1199999999999</v>
+        <v>-644.4799999999999</v>
       </c>
       <c r="F34">
-        <v>660.48</v>
+        <v>681.12</v>
       </c>
       <c r="G34">
         <v>175.2</v>
@@ -4069,28 +4069,28 @@
         <v>329.4</v>
       </c>
       <c r="M34">
-        <v>35.33568</v>
+        <v>36.43992</v>
       </c>
       <c r="N34">
-        <v>294.06432</v>
+        <v>292.9600799999999</v>
       </c>
       <c r="O34">
-        <v>73.51607999999999</v>
+        <v>73.24001999999999</v>
       </c>
       <c r="P34">
-        <v>220.54824</v>
+        <v>219.72006</v>
       </c>
       <c r="Q34">
-        <v>291.64824</v>
+        <v>290.82006</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09009670949104859</v>
+        <v>0.09063568632619276</v>
       </c>
       <c r="T34">
-        <v>0.8878681831488282</v>
+        <v>0.8986712515680629</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.322022386437729</v>
+        <v>9.03953685957598</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07396715983854914</v>
+        <v>0.07382855722318526</v>
       </c>
       <c r="C35">
-        <v>1389.47590180312</v>
+        <v>1378.208729203688</v>
       </c>
       <c r="D35">
-        <v>1895.395901803119</v>
+        <v>1904.768729203688</v>
       </c>
       <c r="E35">
-        <v>-644.4799999999999</v>
+        <v>-623.8399999999998</v>
       </c>
       <c r="F35">
-        <v>681.12</v>
+        <v>701.7600000000001</v>
       </c>
       <c r="G35">
         <v>175.2</v>
@@ -4151,28 +4151,28 @@
         <v>329.4</v>
       </c>
       <c r="M35">
-        <v>36.43992</v>
+        <v>37.54416000000001</v>
       </c>
       <c r="N35">
-        <v>292.9600799999999</v>
+        <v>291.8558399999999</v>
       </c>
       <c r="O35">
-        <v>73.24001999999999</v>
+        <v>72.96395999999999</v>
       </c>
       <c r="P35">
-        <v>219.72006</v>
+        <v>218.89188</v>
       </c>
       <c r="Q35">
-        <v>290.82006</v>
+        <v>289.9918799999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09063568632619276</v>
+        <v>0.09119099579270494</v>
       </c>
       <c r="T35">
-        <v>0.8986712515680629</v>
+        <v>0.9098016856969713</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.03953685957598</v>
+        <v>8.77366812841198</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07382855722318526</v>
+        <v>0.07368995460782136</v>
       </c>
       <c r="C36">
-        <v>1378.208729203688</v>
+        <v>1367.034715478796</v>
       </c>
       <c r="D36">
-        <v>1904.768729203688</v>
+        <v>1914.234715478796</v>
       </c>
       <c r="E36">
-        <v>-623.8399999999998</v>
+        <v>-603.1999999999998</v>
       </c>
       <c r="F36">
-        <v>701.7600000000001</v>
+        <v>722.4000000000001</v>
       </c>
       <c r="G36">
         <v>175.2</v>
@@ -4233,28 +4233,28 @@
         <v>329.4</v>
       </c>
       <c r="M36">
-        <v>37.54416000000001</v>
+        <v>38.6484</v>
       </c>
       <c r="N36">
-        <v>291.8558399999999</v>
+        <v>290.7516</v>
       </c>
       <c r="O36">
-        <v>72.96395999999999</v>
+        <v>72.6879</v>
       </c>
       <c r="P36">
-        <v>218.89188</v>
+        <v>218.0637</v>
       </c>
       <c r="Q36">
-        <v>289.9918799999999</v>
+        <v>289.1636999999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09119099579270494</v>
+        <v>0.09176339170434056</v>
       </c>
       <c r="T36">
-        <v>0.9098016856969713</v>
+        <v>0.9212745947221538</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.77366812841198</v>
+        <v>8.522991896171639</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07368995460782136</v>
+        <v>0.07355135199245745</v>
       </c>
       <c r="C37">
-        <v>1367.034715478796</v>
+        <v>1355.955256459209</v>
       </c>
       <c r="D37">
-        <v>1914.234715478796</v>
+        <v>1923.795256459209</v>
       </c>
       <c r="E37">
-        <v>-603.1999999999998</v>
+        <v>-582.5599999999998</v>
       </c>
       <c r="F37">
-        <v>722.4000000000001</v>
+        <v>743.0400000000001</v>
       </c>
       <c r="G37">
         <v>175.2</v>
@@ -4315,28 +4315,28 @@
         <v>329.4</v>
       </c>
       <c r="M37">
-        <v>38.6484</v>
+        <v>39.75264000000001</v>
       </c>
       <c r="N37">
-        <v>290.7516</v>
+        <v>289.64736</v>
       </c>
       <c r="O37">
-        <v>72.6879</v>
+        <v>72.41184</v>
       </c>
       <c r="P37">
-        <v>218.0637</v>
+        <v>217.23552</v>
       </c>
       <c r="Q37">
-        <v>289.1636999999999</v>
+        <v>288.33552</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09176339170434056</v>
+        <v>0.09235367498821478</v>
       </c>
       <c r="T37">
-        <v>0.9212745947221538</v>
+        <v>0.9331060321543732</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.522991896171639</v>
+        <v>8.286242121277983</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07355135199245746</v>
+        <v>0.07341274937709358</v>
       </c>
       <c r="C38">
-        <v>1355.955256459208</v>
+        <v>1344.971776001267</v>
       </c>
       <c r="D38">
-        <v>1923.795256459208</v>
+        <v>1933.451776001267</v>
       </c>
       <c r="E38">
-        <v>-582.5599999999999</v>
+        <v>-561.92</v>
       </c>
       <c r="F38">
-        <v>743.04</v>
+        <v>763.6799999999999</v>
       </c>
       <c r="G38">
         <v>175.2</v>
@@ -4397,28 +4397,28 @@
         <v>329.4</v>
       </c>
       <c r="M38">
-        <v>39.75264</v>
+        <v>40.85688</v>
       </c>
       <c r="N38">
-        <v>289.64736</v>
+        <v>288.54312</v>
       </c>
       <c r="O38">
-        <v>72.41184</v>
+        <v>72.13578</v>
       </c>
       <c r="P38">
-        <v>217.23552</v>
+        <v>216.40734</v>
       </c>
       <c r="Q38">
-        <v>288.33552</v>
+        <v>287.50734</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09235367498821478</v>
+        <v>0.09296269742395805</v>
       </c>
       <c r="T38">
-        <v>0.9331060321543732</v>
+        <v>0.945313070774917</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.286242121277983</v>
+        <v>8.062289631513714</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07341274937709358</v>
+        <v>0.07327414676172968</v>
       </c>
       <c r="C39">
-        <v>1344.971776001267</v>
+        <v>1334.085726693815</v>
       </c>
       <c r="D39">
-        <v>1933.451776001267</v>
+        <v>1943.205726693815</v>
       </c>
       <c r="E39">
-        <v>-561.92</v>
+        <v>-541.2799999999999</v>
       </c>
       <c r="F39">
-        <v>763.6799999999999</v>
+        <v>784.3200000000001</v>
       </c>
       <c r="G39">
         <v>175.2</v>
@@ -4479,28 +4479,28 @@
         <v>329.4</v>
       </c>
       <c r="M39">
-        <v>40.85688</v>
+        <v>41.96112</v>
       </c>
       <c r="N39">
-        <v>288.54312</v>
+        <v>287.43888</v>
       </c>
       <c r="O39">
-        <v>72.13578</v>
+        <v>71.85972</v>
       </c>
       <c r="P39">
-        <v>216.40734</v>
+        <v>215.57916</v>
       </c>
       <c r="Q39">
-        <v>287.50734</v>
+        <v>286.67916</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09296269742395805</v>
+        <v>0.09359136574472529</v>
       </c>
       <c r="T39">
-        <v>0.945313070774917</v>
+        <v>0.9579138848348333</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.062289631513714</v>
+        <v>7.850124114894931</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07327414676172968</v>
+        <v>0.07313554414636579</v>
       </c>
       <c r="C40">
-        <v>1334.085726693815</v>
+        <v>1323.298590586618</v>
       </c>
       <c r="D40">
-        <v>1943.205726693815</v>
+        <v>1953.058590586618</v>
       </c>
       <c r="E40">
-        <v>-541.2799999999999</v>
+        <v>-520.6399999999999</v>
       </c>
       <c r="F40">
-        <v>784.3200000000001</v>
+        <v>804.96</v>
       </c>
       <c r="G40">
         <v>175.2</v>
@@ -4561,28 +4561,28 @@
         <v>329.4</v>
       </c>
       <c r="M40">
-        <v>41.96112</v>
+        <v>43.06536</v>
       </c>
       <c r="N40">
-        <v>287.43888</v>
+        <v>286.33464</v>
       </c>
       <c r="O40">
-        <v>71.85972</v>
+        <v>71.58365999999999</v>
       </c>
       <c r="P40">
-        <v>215.57916</v>
+        <v>214.75098</v>
       </c>
       <c r="Q40">
-        <v>286.67916</v>
+        <v>285.8509799999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09359136574472529</v>
+        <v>0.09424064614158326</v>
       </c>
       <c r="T40">
-        <v>0.9579138848348333</v>
+        <v>0.9709278403393369</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.850124114894931</v>
+        <v>7.648838881179676</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07313554414636579</v>
+        <v>0.07323694153100188</v>
       </c>
       <c r="C41">
-        <v>1323.298590586618</v>
+        <v>1295.440765928474</v>
       </c>
       <c r="D41">
-        <v>1953.058590586618</v>
+        <v>1945.840765928474</v>
       </c>
       <c r="E41">
-        <v>-520.6399999999999</v>
+        <v>-499.9999999999999</v>
       </c>
       <c r="F41">
-        <v>804.96</v>
+        <v>825.6</v>
       </c>
       <c r="G41">
         <v>175.2</v>
@@ -4643,45 +4643,45 @@
         <v>329.4</v>
       </c>
       <c r="M41">
-        <v>43.06536</v>
+        <v>44.83008</v>
       </c>
       <c r="N41">
-        <v>286.33464</v>
+        <v>284.56992</v>
       </c>
       <c r="O41">
-        <v>71.58365999999999</v>
+        <v>71.14247999999999</v>
       </c>
       <c r="P41">
-        <v>214.75098</v>
+        <v>213.42744</v>
       </c>
       <c r="Q41">
-        <v>285.8509799999999</v>
+        <v>284.52744</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09424064614158326</v>
+        <v>0.09491156921833649</v>
       </c>
       <c r="T41">
-        <v>0.9709278403393369</v>
+        <v>0.9843755943606574</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.648838881179676</v>
+        <v>7.34774508544263</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07323694153100188</v>
+        <v>0.07310433891563799</v>
       </c>
       <c r="C42">
-        <v>1295.440765928474</v>
+        <v>1284.250677000887</v>
       </c>
       <c r="D42">
-        <v>1945.840765928474</v>
+        <v>1955.290677000886</v>
       </c>
       <c r="E42">
-        <v>-499.9999999999999</v>
+        <v>-479.3599999999999</v>
       </c>
       <c r="F42">
-        <v>825.6</v>
+        <v>846.24</v>
       </c>
       <c r="G42">
         <v>175.2</v>
@@ -4725,28 +4725,28 @@
         <v>329.4</v>
       </c>
       <c r="M42">
-        <v>44.83008</v>
+        <v>45.950832</v>
       </c>
       <c r="N42">
-        <v>284.56992</v>
+        <v>283.449168</v>
       </c>
       <c r="O42">
-        <v>71.14247999999999</v>
+        <v>70.862292</v>
       </c>
       <c r="P42">
-        <v>213.42744</v>
+        <v>212.586876</v>
       </c>
       <c r="Q42">
-        <v>284.52744</v>
+        <v>283.686876</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09491156921833649</v>
+        <v>0.09560523545023389</v>
       </c>
       <c r="T42">
-        <v>0.9843755943606574</v>
+        <v>0.9982792044504972</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.34774508544263</v>
+        <v>7.168531790675738</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07310433891563799</v>
+        <v>0.07297173630027411</v>
       </c>
       <c r="C43">
-        <v>1284.250677000887</v>
+        <v>1273.152822364792</v>
       </c>
       <c r="D43">
-        <v>1955.290677000886</v>
+        <v>1964.832822364792</v>
       </c>
       <c r="E43">
-        <v>-479.3599999999999</v>
+        <v>-458.7199999999998</v>
       </c>
       <c r="F43">
-        <v>846.24</v>
+        <v>866.8800000000001</v>
       </c>
       <c r="G43">
         <v>175.2</v>
@@ -4807,28 +4807,28 @@
         <v>329.4</v>
       </c>
       <c r="M43">
-        <v>45.950832</v>
+        <v>47.07158400000001</v>
       </c>
       <c r="N43">
-        <v>283.449168</v>
+        <v>282.3284159999999</v>
       </c>
       <c r="O43">
-        <v>70.862292</v>
+        <v>70.58210399999999</v>
       </c>
       <c r="P43">
-        <v>212.586876</v>
+        <v>211.746312</v>
       </c>
       <c r="Q43">
-        <v>283.686876</v>
+        <v>282.846312</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09560523545023389</v>
+        <v>0.09632282120736915</v>
       </c>
       <c r="T43">
-        <v>0.9982792044504972</v>
+        <v>1.012662249371021</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.168531790675738</v>
+        <v>6.997852462326313</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07297173630027412</v>
+        <v>0.07283913368491021</v>
       </c>
       <c r="C44">
-        <v>1273.152822364791</v>
+        <v>1262.148558998758</v>
       </c>
       <c r="D44">
-        <v>1964.832822364791</v>
+        <v>1974.468558998758</v>
       </c>
       <c r="E44">
-        <v>-458.7199999999999</v>
+        <v>-438.0799999999999</v>
       </c>
       <c r="F44">
-        <v>866.88</v>
+        <v>887.52</v>
       </c>
       <c r="G44">
         <v>175.2</v>
@@ -4889,28 +4889,28 @@
         <v>329.4</v>
       </c>
       <c r="M44">
-        <v>47.071584</v>
+        <v>48.192336</v>
       </c>
       <c r="N44">
-        <v>282.3284159999999</v>
+        <v>281.207664</v>
       </c>
       <c r="O44">
-        <v>70.58210399999999</v>
+        <v>70.30191599999999</v>
       </c>
       <c r="P44">
-        <v>211.746312</v>
+        <v>210.905748</v>
       </c>
       <c r="Q44">
-        <v>282.846312</v>
+        <v>282.0057479999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09632282120736915</v>
+        <v>0.09706558541212316</v>
       </c>
       <c r="T44">
-        <v>1.012662249371021</v>
+        <v>1.02754996253437</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.997852462326314</v>
+        <v>6.835111707388494</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07283913368491021</v>
+        <v>0.07270653106954632</v>
       </c>
       <c r="C45">
-        <v>1262.148558998758</v>
+        <v>1251.239270631569</v>
       </c>
       <c r="D45">
-        <v>1974.468558998758</v>
+        <v>1984.199270631569</v>
       </c>
       <c r="E45">
-        <v>-438.0799999999999</v>
+        <v>-417.4399999999999</v>
       </c>
       <c r="F45">
-        <v>887.52</v>
+        <v>908.16</v>
       </c>
       <c r="G45">
         <v>175.2</v>
@@ -4971,28 +4971,28 @@
         <v>329.4</v>
       </c>
       <c r="M45">
-        <v>48.192336</v>
+        <v>49.313088</v>
       </c>
       <c r="N45">
-        <v>281.207664</v>
+        <v>280.086912</v>
       </c>
       <c r="O45">
-        <v>70.30191599999999</v>
+        <v>70.021728</v>
       </c>
       <c r="P45">
-        <v>210.905748</v>
+        <v>210.065184</v>
       </c>
       <c r="Q45">
-        <v>282.0057479999999</v>
+        <v>281.165184</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09706558541212316</v>
+        <v>0.09783487690990414</v>
       </c>
       <c r="T45">
-        <v>1.02754996253437</v>
+        <v>1.042969379739268</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.835111707388494</v>
+        <v>6.679768259493301</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07270653106954632</v>
+        <v>0.07257392845418241</v>
       </c>
       <c r="C46">
-        <v>1251.239270631569</v>
+        <v>1240.426368404656</v>
       </c>
       <c r="D46">
-        <v>1984.199270631569</v>
+        <v>1994.026368404657</v>
       </c>
       <c r="E46">
-        <v>-417.4399999999999</v>
+        <v>-396.7999999999998</v>
       </c>
       <c r="F46">
-        <v>908.16</v>
+        <v>928.8000000000001</v>
       </c>
       <c r="G46">
         <v>175.2</v>
@@ -5053,28 +5053,28 @@
         <v>329.4</v>
       </c>
       <c r="M46">
-        <v>49.313088</v>
+        <v>50.43384</v>
       </c>
       <c r="N46">
-        <v>280.086912</v>
+        <v>278.9661599999999</v>
       </c>
       <c r="O46">
-        <v>70.021728</v>
+        <v>69.74153999999999</v>
       </c>
       <c r="P46">
-        <v>210.065184</v>
+        <v>209.22462</v>
       </c>
       <c r="Q46">
-        <v>281.165184</v>
+        <v>280.32462</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09783487690990414</v>
+        <v>0.09863214264396802</v>
       </c>
       <c r="T46">
-        <v>1.042969379739268</v>
+        <v>1.058949503024343</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.679768259493301</v>
+        <v>6.531328964837893</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07257392845418241</v>
+        <v>0.07244132583881853</v>
       </c>
       <c r="C47">
-        <v>1240.426368404656</v>
+        <v>1229.711291554304</v>
       </c>
       <c r="D47">
-        <v>1994.026368404657</v>
+        <v>2003.951291554304</v>
       </c>
       <c r="E47">
-        <v>-396.7999999999998</v>
+        <v>-376.1599999999999</v>
       </c>
       <c r="F47">
-        <v>928.8000000000001</v>
+        <v>949.4400000000001</v>
       </c>
       <c r="G47">
         <v>175.2</v>
@@ -5135,28 +5135,28 @@
         <v>329.4</v>
       </c>
       <c r="M47">
-        <v>50.43384</v>
+        <v>51.55459200000001</v>
       </c>
       <c r="N47">
-        <v>278.9661599999999</v>
+        <v>277.845408</v>
       </c>
       <c r="O47">
-        <v>69.74153999999999</v>
+        <v>69.46135199999999</v>
       </c>
       <c r="P47">
-        <v>209.22462</v>
+        <v>208.384056</v>
       </c>
       <c r="Q47">
-        <v>280.32462</v>
+        <v>279.484056</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09863214264396802</v>
+        <v>0.09945893673855283</v>
       </c>
       <c r="T47">
-        <v>1.058949503024343</v>
+        <v>1.075521482727385</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.531328964837893</v>
+        <v>6.389343552558809</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07244132583881853</v>
+        <v>0.07230872322345464</v>
       </c>
       <c r="C48">
-        <v>1229.711291554304</v>
+        <v>1219.09550811434</v>
       </c>
       <c r="D48">
-        <v>2003.951291554304</v>
+        <v>2013.97550811434</v>
       </c>
       <c r="E48">
-        <v>-376.1599999999999</v>
+        <v>-355.5199999999999</v>
       </c>
       <c r="F48">
-        <v>949.4400000000001</v>
+        <v>970.08</v>
       </c>
       <c r="G48">
         <v>175.2</v>
@@ -5217,28 +5217,28 @@
         <v>329.4</v>
       </c>
       <c r="M48">
-        <v>51.55459200000001</v>
+        <v>52.675344</v>
       </c>
       <c r="N48">
-        <v>277.845408</v>
+        <v>276.724656</v>
       </c>
       <c r="O48">
-        <v>69.46135199999999</v>
+        <v>69.181164</v>
       </c>
       <c r="P48">
-        <v>208.384056</v>
+        <v>207.543492</v>
       </c>
       <c r="Q48">
-        <v>279.484056</v>
+        <v>278.643492</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09945893673855283</v>
+        <v>0.1003169306102918</v>
       </c>
       <c r="T48">
-        <v>1.075521482727385</v>
+        <v>1.092718820155069</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.389343552558809</v>
+        <v>6.253400072717133</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07230872322345464</v>
+        <v>0.07217612060809074</v>
       </c>
       <c r="C49">
-        <v>1219.09550811434</v>
+        <v>1208.580515640006</v>
       </c>
       <c r="D49">
-        <v>2013.97550811434</v>
+        <v>2024.100515640006</v>
       </c>
       <c r="E49">
-        <v>-355.5199999999999</v>
+        <v>-334.8799999999999</v>
       </c>
       <c r="F49">
-        <v>970.08</v>
+        <v>990.72</v>
       </c>
       <c r="G49">
         <v>175.2</v>
@@ -5299,28 +5299,28 @@
         <v>329.4</v>
       </c>
       <c r="M49">
-        <v>52.675344</v>
+        <v>53.79609600000001</v>
       </c>
       <c r="N49">
-        <v>276.724656</v>
+        <v>275.6039039999999</v>
       </c>
       <c r="O49">
-        <v>69.181164</v>
+        <v>68.90097599999999</v>
       </c>
       <c r="P49">
-        <v>207.543492</v>
+        <v>206.702928</v>
       </c>
       <c r="Q49">
-        <v>278.643492</v>
+        <v>277.802928</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1003169306102918</v>
+        <v>0.1012079242463284</v>
       </c>
       <c r="T49">
-        <v>1.092718820155069</v>
+        <v>1.110577593637665</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.253400072717133</v>
+        <v>6.123120904535525</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07217612060809074</v>
+        <v>0.07241101799272684</v>
       </c>
       <c r="C50">
-        <v>1208.580515640006</v>
+        <v>1170.073633678016</v>
       </c>
       <c r="D50">
-        <v>2024.100515640006</v>
+        <v>2006.233633678017</v>
       </c>
       <c r="E50">
-        <v>-334.88</v>
+        <v>-314.2399999999999</v>
       </c>
       <c r="F50">
-        <v>990.7199999999999</v>
+        <v>1011.36</v>
       </c>
       <c r="G50">
         <v>175.2</v>
@@ -5381,45 +5381,45 @@
         <v>329.4</v>
       </c>
       <c r="M50">
-        <v>53.796096</v>
+        <v>55.92820800000001</v>
       </c>
       <c r="N50">
-        <v>275.603904</v>
+        <v>273.471792</v>
       </c>
       <c r="O50">
-        <v>68.900976</v>
+        <v>68.367948</v>
       </c>
       <c r="P50">
-        <v>206.702928</v>
+        <v>205.103844</v>
       </c>
       <c r="Q50">
-        <v>277.802928</v>
+        <v>276.203844</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1012079242463284</v>
+        <v>0.1021338588092683</v>
       </c>
       <c r="T50">
-        <v>1.110577593637665</v>
+        <v>1.129136711178401</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.123120904535527</v>
+        <v>5.889693444138242</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07241101799272684</v>
+        <v>0.07228591537736295</v>
       </c>
       <c r="C51">
-        <v>1170.073633678016</v>
+        <v>1158.909805108309</v>
       </c>
       <c r="D51">
-        <v>2006.233633678017</v>
+        <v>2015.709805108309</v>
       </c>
       <c r="E51">
-        <v>-314.2399999999999</v>
+        <v>-293.5999999999999</v>
       </c>
       <c r="F51">
-        <v>1011.36</v>
+        <v>1032</v>
       </c>
       <c r="G51">
         <v>175.2</v>
@@ -5463,28 +5463,28 @@
         <v>329.4</v>
       </c>
       <c r="M51">
-        <v>55.92820800000001</v>
+        <v>57.0696</v>
       </c>
       <c r="N51">
-        <v>273.471792</v>
+        <v>272.3304</v>
       </c>
       <c r="O51">
-        <v>68.367948</v>
+        <v>68.0826</v>
       </c>
       <c r="P51">
-        <v>205.103844</v>
+        <v>204.2478</v>
       </c>
       <c r="Q51">
-        <v>276.203844</v>
+        <v>275.3478</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1021338588092683</v>
+        <v>0.1030968307547259</v>
       </c>
       <c r="T51">
-        <v>1.129136711178401</v>
+        <v>1.148438193420767</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.889693444138242</v>
+        <v>5.771899575255477</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07228591537736295</v>
+        <v>0.07216081276199905</v>
       </c>
       <c r="C52">
-        <v>1158.909805108309</v>
+        <v>1147.835920186416</v>
       </c>
       <c r="D52">
-        <v>2015.709805108309</v>
+        <v>2025.275920186416</v>
       </c>
       <c r="E52">
-        <v>-293.5999999999999</v>
+        <v>-272.9599999999998</v>
       </c>
       <c r="F52">
-        <v>1032</v>
+        <v>1052.64</v>
       </c>
       <c r="G52">
         <v>175.2</v>
@@ -5545,28 +5545,28 @@
         <v>329.4</v>
       </c>
       <c r="M52">
-        <v>57.0696</v>
+        <v>58.210992</v>
       </c>
       <c r="N52">
-        <v>272.3304</v>
+        <v>271.1890079999999</v>
       </c>
       <c r="O52">
-        <v>68.0826</v>
+        <v>67.79725199999999</v>
       </c>
       <c r="P52">
-        <v>204.2478</v>
+        <v>203.391756</v>
       </c>
       <c r="Q52">
-        <v>275.3478</v>
+        <v>274.491756</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1030968307547259</v>
+        <v>0.1040991076775491</v>
       </c>
       <c r="T52">
-        <v>1.148438193420767</v>
+        <v>1.168527491264862</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.771899575255477</v>
+        <v>5.658725073779879</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07216081276199905</v>
+        <v>0.07203571014663515</v>
       </c>
       <c r="C53">
-        <v>1147.835920186416</v>
+        <v>1136.85326557683</v>
       </c>
       <c r="D53">
-        <v>2025.275920186416</v>
+        <v>2034.93326557683</v>
       </c>
       <c r="E53">
-        <v>-272.9599999999998</v>
+        <v>-252.3199999999999</v>
       </c>
       <c r="F53">
-        <v>1052.64</v>
+        <v>1073.28</v>
       </c>
       <c r="G53">
         <v>175.2</v>
@@ -5627,28 +5627,28 @@
         <v>329.4</v>
       </c>
       <c r="M53">
-        <v>58.210992</v>
+        <v>59.352384</v>
       </c>
       <c r="N53">
-        <v>271.1890079999999</v>
+        <v>270.0476159999999</v>
       </c>
       <c r="O53">
-        <v>67.79725199999999</v>
+        <v>67.51190399999999</v>
       </c>
       <c r="P53">
-        <v>203.391756</v>
+        <v>202.535712</v>
       </c>
       <c r="Q53">
-        <v>274.491756</v>
+        <v>273.635712</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1040991076775491</v>
+        <v>0.1051431461388233</v>
       </c>
       <c r="T53">
-        <v>1.168527491264862</v>
+        <v>1.189453843185794</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.658725073779879</v>
+        <v>5.549903437745651</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07203571014663515</v>
+        <v>0.07191060753127126</v>
       </c>
       <c r="C54">
-        <v>1136.85326557683</v>
+        <v>1125.963152603003</v>
       </c>
       <c r="D54">
-        <v>2034.93326557683</v>
+        <v>2044.683152603003</v>
       </c>
       <c r="E54">
-        <v>-252.3199999999999</v>
+        <v>-231.6799999999998</v>
       </c>
       <c r="F54">
-        <v>1073.28</v>
+        <v>1093.92</v>
       </c>
       <c r="G54">
         <v>175.2</v>
@@ -5709,28 +5709,28 @@
         <v>329.4</v>
       </c>
       <c r="M54">
-        <v>59.352384</v>
+        <v>60.493776</v>
       </c>
       <c r="N54">
-        <v>270.0476159999999</v>
+        <v>268.906224</v>
       </c>
       <c r="O54">
-        <v>67.51190399999999</v>
+        <v>67.22655599999999</v>
       </c>
       <c r="P54">
-        <v>202.535712</v>
+        <v>201.679668</v>
       </c>
       <c r="Q54">
-        <v>273.635712</v>
+        <v>272.779668</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1051431461388233</v>
+        <v>0.1062316117686623</v>
       </c>
       <c r="T54">
-        <v>1.189453843185794</v>
+        <v>1.211270678167192</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.549903437745651</v>
+        <v>5.445188278542902</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07191060753127126</v>
+        <v>0.07178550491590738</v>
       </c>
       <c r="C55">
-        <v>1125.963152603003</v>
+        <v>1115.166917840927</v>
       </c>
       <c r="D55">
-        <v>2044.683152603003</v>
+        <v>2054.526917840927</v>
       </c>
       <c r="E55">
-        <v>-231.6799999999998</v>
+        <v>-211.0399999999997</v>
       </c>
       <c r="F55">
-        <v>1093.92</v>
+        <v>1114.56</v>
       </c>
       <c r="G55">
         <v>175.2</v>
@@ -5791,28 +5791,28 @@
         <v>329.4</v>
       </c>
       <c r="M55">
-        <v>60.493776</v>
+        <v>61.63516800000001</v>
       </c>
       <c r="N55">
-        <v>268.906224</v>
+        <v>267.764832</v>
       </c>
       <c r="O55">
-        <v>67.22655599999999</v>
+        <v>66.94120799999999</v>
       </c>
       <c r="P55">
-        <v>201.679668</v>
+        <v>200.823624</v>
       </c>
       <c r="Q55">
-        <v>272.779668</v>
+        <v>271.923624</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1062316117686623</v>
+        <v>0.107367401991103</v>
       </c>
       <c r="T55">
-        <v>1.211270678167192</v>
+        <v>1.234036071191259</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.445188278542902</v>
+        <v>5.344351458569885</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07178550491590738</v>
+        <v>0.07166040230054349</v>
       </c>
       <c r="C56">
-        <v>1115.166917840927</v>
+        <v>1104.465923729942</v>
       </c>
       <c r="D56">
-        <v>2054.526917840927</v>
+        <v>2064.465923729942</v>
       </c>
       <c r="E56">
-        <v>-211.0399999999997</v>
+        <v>-190.3999999999999</v>
       </c>
       <c r="F56">
-        <v>1114.56</v>
+        <v>1135.2</v>
       </c>
       <c r="G56">
         <v>175.2</v>
@@ -5873,28 +5873,28 @@
         <v>329.4</v>
       </c>
       <c r="M56">
-        <v>61.63516800000001</v>
+        <v>62.77656</v>
       </c>
       <c r="N56">
-        <v>267.764832</v>
+        <v>266.62344</v>
       </c>
       <c r="O56">
-        <v>66.94120799999999</v>
+        <v>66.65585999999999</v>
       </c>
       <c r="P56">
-        <v>200.823624</v>
+        <v>199.96758</v>
       </c>
       <c r="Q56">
-        <v>271.923624</v>
+        <v>271.06758</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.107367401991103</v>
+        <v>0.1085536717789855</v>
       </c>
       <c r="T56">
-        <v>1.234036071191259</v>
+        <v>1.25781325946084</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.344351458569885</v>
+        <v>5.247181432050433</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07166040230054349</v>
+        <v>0.07153529968517958</v>
       </c>
       <c r="C57">
-        <v>1104.465923729942</v>
+        <v>1093.861559201365</v>
       </c>
       <c r="D57">
-        <v>2064.465923729942</v>
+        <v>2074.501559201366</v>
       </c>
       <c r="E57">
-        <v>-190.3999999999999</v>
+        <v>-169.7599999999998</v>
       </c>
       <c r="F57">
-        <v>1135.2</v>
+        <v>1155.84</v>
       </c>
       <c r="G57">
         <v>175.2</v>
@@ -5955,28 +5955,28 @@
         <v>329.4</v>
       </c>
       <c r="M57">
-        <v>62.77656</v>
+        <v>63.91795200000001</v>
       </c>
       <c r="N57">
-        <v>266.62344</v>
+        <v>265.482048</v>
       </c>
       <c r="O57">
-        <v>66.65585999999999</v>
+        <v>66.37051199999999</v>
       </c>
       <c r="P57">
-        <v>199.96758</v>
+        <v>199.111536</v>
       </c>
       <c r="Q57">
-        <v>271.06758</v>
+        <v>270.211536</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1085536717789855</v>
+        <v>0.1097938629208627</v>
       </c>
       <c r="T57">
-        <v>1.25781325946084</v>
+        <v>1.282671229015402</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.247181432050433</v>
+        <v>5.153481763620961</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07153529968517958</v>
+        <v>0.07141019706981569</v>
       </c>
       <c r="C58">
-        <v>1093.861559201365</v>
+        <v>1083.355240325531</v>
       </c>
       <c r="D58">
-        <v>2074.501559201366</v>
+        <v>2084.635240325531</v>
       </c>
       <c r="E58">
-        <v>-169.7599999999998</v>
+        <v>-149.1199999999999</v>
       </c>
       <c r="F58">
-        <v>1155.84</v>
+        <v>1176.48</v>
       </c>
       <c r="G58">
         <v>175.2</v>
@@ -6037,28 +6037,28 @@
         <v>329.4</v>
       </c>
       <c r="M58">
-        <v>63.91795200000001</v>
+        <v>65.05934400000001</v>
       </c>
       <c r="N58">
-        <v>265.482048</v>
+        <v>264.340656</v>
       </c>
       <c r="O58">
-        <v>66.37051199999999</v>
+        <v>66.08516399999999</v>
       </c>
       <c r="P58">
-        <v>199.111536</v>
+        <v>198.255492</v>
       </c>
       <c r="Q58">
-        <v>270.211536</v>
+        <v>269.355492</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1097938629208627</v>
+        <v>0.1110917373716644</v>
       </c>
       <c r="T58">
-        <v>1.282671229015402</v>
+        <v>1.308685383200409</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.153481763620961</v>
+        <v>5.063069802855681</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07141019706981569</v>
+        <v>0.0712850944544518</v>
       </c>
       <c r="C59">
-        <v>1083.355240325531</v>
+        <v>1072.948410977912</v>
       </c>
       <c r="D59">
-        <v>2084.635240325531</v>
+        <v>2094.868410977912</v>
       </c>
       <c r="E59">
-        <v>-149.1199999999999</v>
+        <v>-128.4799999999998</v>
       </c>
       <c r="F59">
-        <v>1176.48</v>
+        <v>1197.12</v>
       </c>
       <c r="G59">
         <v>175.2</v>
@@ -6119,28 +6119,28 @@
         <v>329.4</v>
       </c>
       <c r="M59">
-        <v>65.05934400000001</v>
+        <v>66.20073600000001</v>
       </c>
       <c r="N59">
-        <v>264.340656</v>
+        <v>263.199264</v>
       </c>
       <c r="O59">
-        <v>66.08516399999999</v>
+        <v>65.79981599999999</v>
       </c>
       <c r="P59">
-        <v>198.255492</v>
+        <v>197.399448</v>
       </c>
       <c r="Q59">
-        <v>269.355492</v>
+        <v>268.499448</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1110917373716644</v>
+        <v>0.1124514153677424</v>
       </c>
       <c r="T59">
-        <v>1.308685383200409</v>
+        <v>1.335938306632321</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.063069802855681</v>
+        <v>4.975775495909893</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07128509445445179</v>
+        <v>0.07115999183908792</v>
       </c>
       <c r="C60">
-        <v>1072.948410977913</v>
+        <v>1062.642543524934</v>
       </c>
       <c r="D60">
-        <v>2094.868410977913</v>
+        <v>2105.202543524934</v>
       </c>
       <c r="E60">
-        <v>-128.48</v>
+        <v>-107.8399999999999</v>
       </c>
       <c r="F60">
-        <v>1197.12</v>
+        <v>1217.76</v>
       </c>
       <c r="G60">
         <v>175.2</v>
@@ -6201,28 +6201,28 @@
         <v>329.4</v>
       </c>
       <c r="M60">
-        <v>66.20073599999999</v>
+        <v>67.342128</v>
       </c>
       <c r="N60">
-        <v>263.199264</v>
+        <v>262.057872</v>
       </c>
       <c r="O60">
-        <v>65.79981599999999</v>
+        <v>65.51446799999999</v>
       </c>
       <c r="P60">
-        <v>197.399448</v>
+        <v>196.543404</v>
       </c>
       <c r="Q60">
-        <v>268.499448</v>
+        <v>267.643404</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1124514153677424</v>
+        <v>0.1138774191197266</v>
       </c>
       <c r="T60">
-        <v>1.335938306632321</v>
+        <v>1.36452064096335</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.975775495909895</v>
+        <v>4.891440318013116</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07115999183908792</v>
+        <v>0.071034889223724</v>
       </c>
       <c r="C61">
-        <v>1062.642543524934</v>
+        <v>1052.439139530203</v>
       </c>
       <c r="D61">
-        <v>2105.202543524934</v>
+        <v>2115.639139530203</v>
       </c>
       <c r="E61">
-        <v>-107.8399999999999</v>
+        <v>-87.20000000000005</v>
       </c>
       <c r="F61">
-        <v>1217.76</v>
+        <v>1238.4</v>
       </c>
       <c r="G61">
         <v>175.2</v>
@@ -6283,28 +6283,28 @@
         <v>329.4</v>
       </c>
       <c r="M61">
-        <v>67.342128</v>
+        <v>68.48352</v>
       </c>
       <c r="N61">
-        <v>262.057872</v>
+        <v>260.91648</v>
       </c>
       <c r="O61">
-        <v>65.51446799999999</v>
+        <v>65.22911999999999</v>
       </c>
       <c r="P61">
-        <v>196.543404</v>
+        <v>195.68736</v>
       </c>
       <c r="Q61">
-        <v>267.643404</v>
+        <v>266.78736</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1138774191197266</v>
+        <v>0.11537472305931</v>
       </c>
       <c r="T61">
-        <v>1.36452064096335</v>
+        <v>1.394532092010931</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.891440318013116</v>
+        <v>4.809916312712898</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.071034889223724</v>
+        <v>0.07090978660836013</v>
       </c>
       <c r="C62">
-        <v>1052.439139530203</v>
+        <v>1042.339730481832</v>
       </c>
       <c r="D62">
-        <v>2115.639139530203</v>
+        <v>2126.179730481832</v>
       </c>
       <c r="E62">
-        <v>-87.20000000000005</v>
+        <v>-66.55999999999995</v>
       </c>
       <c r="F62">
-        <v>1238.4</v>
+        <v>1259.04</v>
       </c>
       <c r="G62">
         <v>175.2</v>
@@ -6365,28 +6365,28 @@
         <v>329.4</v>
       </c>
       <c r="M62">
-        <v>68.48352</v>
+        <v>69.62491199999999</v>
       </c>
       <c r="N62">
-        <v>260.91648</v>
+        <v>259.775088</v>
       </c>
       <c r="O62">
-        <v>65.22911999999999</v>
+        <v>64.943772</v>
       </c>
       <c r="P62">
-        <v>195.68736</v>
+        <v>194.831316</v>
       </c>
       <c r="Q62">
-        <v>266.78736</v>
+        <v>265.931316</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.11537472305931</v>
+        <v>0.116948811816308</v>
       </c>
       <c r="T62">
-        <v>1.394532092010931</v>
+        <v>1.426082591830183</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.809916312712898</v>
+        <v>4.731065225619243</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07090978660836013</v>
+        <v>0.07078468399299621</v>
       </c>
       <c r="C63">
-        <v>1042.339730481832</v>
+        <v>1032.345878541643</v>
       </c>
       <c r="D63">
-        <v>2126.179730481832</v>
+        <v>2136.825878541643</v>
       </c>
       <c r="E63">
-        <v>-66.55999999999995</v>
+        <v>-45.91999999999985</v>
       </c>
       <c r="F63">
-        <v>1259.04</v>
+        <v>1279.68</v>
       </c>
       <c r="G63">
         <v>175.2</v>
@@ -6447,28 +6447,28 @@
         <v>329.4</v>
       </c>
       <c r="M63">
-        <v>69.62491199999999</v>
+        <v>70.76630400000001</v>
       </c>
       <c r="N63">
-        <v>259.775088</v>
+        <v>258.633696</v>
       </c>
       <c r="O63">
-        <v>64.943772</v>
+        <v>64.658424</v>
       </c>
       <c r="P63">
-        <v>194.831316</v>
+        <v>193.975272</v>
       </c>
       <c r="Q63">
-        <v>265.931316</v>
+        <v>265.075272</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.116948811816308</v>
+        <v>0.11860574734999</v>
       </c>
       <c r="T63">
-        <v>1.426082591830183</v>
+        <v>1.459293644271501</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.731065225619243</v>
+        <v>4.654757721980223</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07078468399299621</v>
+        <v>0.07065958137763231</v>
       </c>
       <c r="C64">
-        <v>1032.345878541643</v>
+        <v>1022.459177316953</v>
       </c>
       <c r="D64">
-        <v>2136.825878541643</v>
+        <v>2147.579177316953</v>
       </c>
       <c r="E64">
-        <v>-45.91999999999985</v>
+        <v>-25.27999999999997</v>
       </c>
       <c r="F64">
-        <v>1279.68</v>
+        <v>1300.32</v>
       </c>
       <c r="G64">
         <v>175.2</v>
@@ -6529,28 +6529,28 @@
         <v>329.4</v>
       </c>
       <c r="M64">
-        <v>70.76630400000001</v>
+        <v>71.907696</v>
       </c>
       <c r="N64">
-        <v>258.633696</v>
+        <v>257.492304</v>
       </c>
       <c r="O64">
-        <v>64.658424</v>
+        <v>64.373076</v>
       </c>
       <c r="P64">
-        <v>193.975272</v>
+        <v>193.119228</v>
       </c>
       <c r="Q64">
-        <v>265.075272</v>
+        <v>264.219228</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.11860574734999</v>
+        <v>0.1203522469665738</v>
       </c>
       <c r="T64">
-        <v>1.459293644271501</v>
+        <v>1.494299888736674</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.654757721980223</v>
+        <v>4.580872678774188</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07065958137763231</v>
+        <v>0.07053447876226843</v>
       </c>
       <c r="C65">
-        <v>1022.459177316953</v>
+        <v>1012.68125265582</v>
       </c>
       <c r="D65">
-        <v>2147.579177316953</v>
+        <v>2158.44125265582</v>
       </c>
       <c r="E65">
-        <v>-25.27999999999997</v>
+        <v>-4.639999999999873</v>
       </c>
       <c r="F65">
-        <v>1300.32</v>
+        <v>1320.96</v>
       </c>
       <c r="G65">
         <v>175.2</v>
@@ -6611,28 +6611,28 @@
         <v>329.4</v>
       </c>
       <c r="M65">
-        <v>71.907696</v>
+        <v>73.049088</v>
       </c>
       <c r="N65">
-        <v>257.492304</v>
+        <v>256.350912</v>
       </c>
       <c r="O65">
-        <v>64.373076</v>
+        <v>64.087728</v>
       </c>
       <c r="P65">
-        <v>193.119228</v>
+        <v>192.263184</v>
       </c>
       <c r="Q65">
-        <v>264.219228</v>
+        <v>263.363184</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1203522469665738</v>
+        <v>0.1221957743396345</v>
       </c>
       <c r="T65">
-        <v>1.494299888736674</v>
+        <v>1.531250924561023</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.580872678774188</v>
+        <v>4.509296543168341</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07053447876226843</v>
+        <v>0.07162812614690453</v>
       </c>
       <c r="C66">
-        <v>1012.68125265582</v>
+        <v>900.6457864330171</v>
       </c>
       <c r="D66">
-        <v>2158.44125265582</v>
+        <v>2067.045786433017</v>
       </c>
       <c r="E66">
-        <v>-4.639999999999873</v>
+        <v>16.00000000000023</v>
       </c>
       <c r="F66">
-        <v>1320.96</v>
+        <v>1341.6</v>
       </c>
       <c r="G66">
         <v>175.2</v>
@@ -6693,45 +6693,45 @@
         <v>329.4</v>
       </c>
       <c r="M66">
-        <v>73.049088</v>
+        <v>77.54448000000001</v>
       </c>
       <c r="N66">
-        <v>256.350912</v>
+        <v>251.85552</v>
       </c>
       <c r="O66">
-        <v>64.087728</v>
+        <v>62.96387999999999</v>
       </c>
       <c r="P66">
-        <v>192.263184</v>
+        <v>188.89164</v>
       </c>
       <c r="Q66">
-        <v>263.363184</v>
+        <v>259.99164</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1221957743396345</v>
+        <v>0.124144646134013</v>
       </c>
       <c r="T66">
-        <v>1.531250924561023</v>
+        <v>1.570313448146763</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.509296543168341</v>
+        <v>4.247884568959647</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07162812614690453</v>
+        <v>0.07152177353154064</v>
       </c>
       <c r="C67">
-        <v>900.6457864330171</v>
+        <v>888.552464802395</v>
       </c>
       <c r="D67">
-        <v>2067.045786433017</v>
+        <v>2075.592464802395</v>
       </c>
       <c r="E67">
-        <v>16.00000000000023</v>
+        <v>36.6400000000001</v>
       </c>
       <c r="F67">
-        <v>1341.6</v>
+        <v>1362.24</v>
       </c>
       <c r="G67">
         <v>175.2</v>
@@ -6775,28 +6775,28 @@
         <v>329.4</v>
       </c>
       <c r="M67">
-        <v>77.54448000000001</v>
+        <v>78.73747200000001</v>
       </c>
       <c r="N67">
-        <v>251.85552</v>
+        <v>250.662528</v>
       </c>
       <c r="O67">
-        <v>62.96387999999999</v>
+        <v>62.66563199999999</v>
       </c>
       <c r="P67">
-        <v>188.89164</v>
+        <v>187.996896</v>
       </c>
       <c r="Q67">
-        <v>259.99164</v>
+        <v>259.096896</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.124144646134013</v>
+        <v>0.1262081574457078</v>
       </c>
       <c r="T67">
-        <v>1.570313448146763</v>
+        <v>1.611673767237547</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.247884568959647</v>
+        <v>4.183522681551167</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07152177353154064</v>
+        <v>0.07141542091617674</v>
       </c>
       <c r="C68">
-        <v>888.552464802395</v>
+        <v>876.5301130457601</v>
       </c>
       <c r="D68">
-        <v>2075.592464802395</v>
+        <v>2084.21011304576</v>
       </c>
       <c r="E68">
-        <v>36.6400000000001</v>
+        <v>57.2800000000002</v>
       </c>
       <c r="F68">
-        <v>1362.24</v>
+        <v>1382.88</v>
       </c>
       <c r="G68">
         <v>175.2</v>
@@ -6857,28 +6857,28 @@
         <v>329.4</v>
       </c>
       <c r="M68">
-        <v>78.73747200000001</v>
+        <v>79.93046400000001</v>
       </c>
       <c r="N68">
-        <v>250.662528</v>
+        <v>249.4695359999999</v>
       </c>
       <c r="O68">
-        <v>62.66563199999999</v>
+        <v>62.36738399999999</v>
       </c>
       <c r="P68">
-        <v>187.996896</v>
+        <v>187.102152</v>
       </c>
       <c r="Q68">
-        <v>259.096896</v>
+        <v>258.202152</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1262081574457078</v>
+        <v>0.1283967300490204</v>
       </c>
       <c r="T68">
-        <v>1.611673767237547</v>
+        <v>1.655540772333833</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.183522681551167</v>
+        <v>4.12108204451309</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07141542091617674</v>
+        <v>0.07130906830081285</v>
       </c>
       <c r="C69">
-        <v>876.5301130457601</v>
+        <v>864.5796188276393</v>
       </c>
       <c r="D69">
-        <v>2084.21011304576</v>
+        <v>2092.89961882764</v>
       </c>
       <c r="E69">
-        <v>57.2800000000002</v>
+        <v>77.9200000000003</v>
       </c>
       <c r="F69">
-        <v>1382.88</v>
+        <v>1403.52</v>
       </c>
       <c r="G69">
         <v>175.2</v>
@@ -6939,28 +6939,28 @@
         <v>329.4</v>
       </c>
       <c r="M69">
-        <v>79.93046400000001</v>
+        <v>81.12345600000002</v>
       </c>
       <c r="N69">
-        <v>249.4695359999999</v>
+        <v>248.2765439999999</v>
       </c>
       <c r="O69">
-        <v>62.36738399999999</v>
+        <v>62.06913599999999</v>
       </c>
       <c r="P69">
-        <v>187.102152</v>
+        <v>186.207408</v>
       </c>
       <c r="Q69">
-        <v>258.202152</v>
+        <v>257.307408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1283967300490204</v>
+        <v>0.1307220884400402</v>
       </c>
       <c r="T69">
-        <v>1.655540772333833</v>
+        <v>1.702149465248637</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.12108204451309</v>
+        <v>4.060477896799662</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07130906830081285</v>
+        <v>0.07120271568544895</v>
       </c>
       <c r="C70">
-        <v>864.5796188276393</v>
+        <v>852.7018846779772</v>
       </c>
       <c r="D70">
-        <v>2092.89961882764</v>
+        <v>2101.661884677977</v>
       </c>
       <c r="E70">
-        <v>77.9200000000003</v>
+        <v>98.56000000000017</v>
       </c>
       <c r="F70">
-        <v>1403.52</v>
+        <v>1424.16</v>
       </c>
       <c r="G70">
         <v>175.2</v>
@@ -7021,28 +7021,28 @@
         <v>329.4</v>
       </c>
       <c r="M70">
-        <v>81.12345600000002</v>
+        <v>82.31644800000001</v>
       </c>
       <c r="N70">
-        <v>248.2765439999999</v>
+        <v>247.083552</v>
       </c>
       <c r="O70">
-        <v>62.06913599999999</v>
+        <v>61.77088799999999</v>
       </c>
       <c r="P70">
-        <v>186.207408</v>
+        <v>185.312664</v>
       </c>
       <c r="Q70">
-        <v>257.307408</v>
+        <v>256.4126639999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1307220884400402</v>
+        <v>0.1331974699530612</v>
       </c>
       <c r="T70">
-        <v>1.702149465248637</v>
+        <v>1.751765170609557</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.060477896799662</v>
+        <v>4.001630391048943</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07120271568544895</v>
+        <v>0.07293386307008506</v>
       </c>
       <c r="C71">
-        <v>852.7018846779772</v>
+        <v>697.9753203855198</v>
       </c>
       <c r="D71">
-        <v>2101.661884677977</v>
+        <v>1967.57532038552</v>
       </c>
       <c r="E71">
-        <v>98.56000000000017</v>
+        <v>119.2000000000003</v>
       </c>
       <c r="F71">
-        <v>1424.16</v>
+        <v>1444.8</v>
       </c>
       <c r="G71">
         <v>175.2</v>
@@ -7103,45 +7103,45 @@
         <v>329.4</v>
       </c>
       <c r="M71">
-        <v>82.31644800000001</v>
+        <v>88.56624000000001</v>
       </c>
       <c r="N71">
-        <v>247.083552</v>
+        <v>240.83376</v>
       </c>
       <c r="O71">
-        <v>61.77088799999999</v>
+        <v>60.20844</v>
       </c>
       <c r="P71">
-        <v>185.312664</v>
+        <v>180.62532</v>
       </c>
       <c r="Q71">
-        <v>256.4126639999999</v>
+        <v>251.72532</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1331974699530612</v>
+        <v>0.1358378769002836</v>
       </c>
       <c r="T71">
-        <v>1.751765170609557</v>
+        <v>1.804688589661205</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.001630391048943</v>
+        <v>3.71925013413689</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07293386307008506</v>
+        <v>0.07285376045472117</v>
       </c>
       <c r="C72">
-        <v>697.9753203855198</v>
+        <v>683.1610513167939</v>
       </c>
       <c r="D72">
-        <v>1967.57532038552</v>
+        <v>1973.401051316794</v>
       </c>
       <c r="E72">
-        <v>119.2000000000003</v>
+        <v>139.8400000000001</v>
       </c>
       <c r="F72">
-        <v>1444.8</v>
+        <v>1465.44</v>
       </c>
       <c r="G72">
         <v>175.2</v>
@@ -7185,28 +7185,28 @@
         <v>329.4</v>
       </c>
       <c r="M72">
-        <v>88.56624000000001</v>
+        <v>89.83147200000001</v>
       </c>
       <c r="N72">
-        <v>240.83376</v>
+        <v>239.568528</v>
       </c>
       <c r="O72">
-        <v>60.20844</v>
+        <v>59.89213199999999</v>
       </c>
       <c r="P72">
-        <v>180.62532</v>
+        <v>179.676396</v>
       </c>
       <c r="Q72">
-        <v>251.72532</v>
+        <v>250.7763959999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1358378769002836</v>
+        <v>0.1386603808783489</v>
       </c>
       <c r="T72">
-        <v>1.804688589661205</v>
+        <v>1.861261899681933</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.71925013413689</v>
+        <v>3.666866329430736</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07285376045472117</v>
+        <v>0.07277365783935727</v>
       </c>
       <c r="C73">
-        <v>683.1610513167941</v>
+        <v>668.3813831380749</v>
       </c>
       <c r="D73">
-        <v>1973.401051316794</v>
+        <v>1979.261383138075</v>
       </c>
       <c r="E73">
-        <v>139.8399999999999</v>
+        <v>160.48</v>
       </c>
       <c r="F73">
-        <v>1465.44</v>
+        <v>1486.08</v>
       </c>
       <c r="G73">
         <v>175.2</v>
@@ -7267,28 +7267,28 @@
         <v>329.4</v>
       </c>
       <c r="M73">
-        <v>89.83147199999999</v>
+        <v>91.096704</v>
       </c>
       <c r="N73">
-        <v>239.568528</v>
+        <v>238.303296</v>
       </c>
       <c r="O73">
-        <v>59.892132</v>
+        <v>59.575824</v>
       </c>
       <c r="P73">
-        <v>179.676396</v>
+        <v>178.727472</v>
       </c>
       <c r="Q73">
-        <v>250.776396</v>
+        <v>249.827472</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1386603808783489</v>
+        <v>0.1416844922834188</v>
       </c>
       <c r="T73">
-        <v>1.861261899681933</v>
+        <v>1.921876160418426</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.666866329430737</v>
+        <v>3.615937630410865</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07277365783935727</v>
+        <v>0.07269355522399339</v>
       </c>
       <c r="C74">
-        <v>668.3813831380749</v>
+        <v>653.6366250262374</v>
       </c>
       <c r="D74">
-        <v>1979.261383138075</v>
+        <v>1985.156625026237</v>
       </c>
       <c r="E74">
-        <v>160.48</v>
+        <v>181.1200000000001</v>
       </c>
       <c r="F74">
-        <v>1486.08</v>
+        <v>1506.72</v>
       </c>
       <c r="G74">
         <v>175.2</v>
@@ -7349,28 +7349,28 @@
         <v>329.4</v>
       </c>
       <c r="M74">
-        <v>91.096704</v>
+        <v>92.361936</v>
       </c>
       <c r="N74">
-        <v>238.303296</v>
+        <v>237.038064</v>
       </c>
       <c r="O74">
-        <v>59.575824</v>
+        <v>59.25951599999999</v>
       </c>
       <c r="P74">
-        <v>178.727472</v>
+        <v>177.778548</v>
       </c>
       <c r="Q74">
-        <v>249.827472</v>
+        <v>248.878548</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1416844922834188</v>
+        <v>0.1449326119407162</v>
       </c>
       <c r="T74">
-        <v>1.921876160418426</v>
+        <v>1.98698036639466</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.615937630410865</v>
+        <v>3.566404238213456</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07269355522399339</v>
+        <v>0.0726134526086295</v>
       </c>
       <c r="C75">
-        <v>653.6366250262374</v>
+        <v>638.9270898527013</v>
       </c>
       <c r="D75">
-        <v>1985.156625026237</v>
+        <v>1991.087089852701</v>
       </c>
       <c r="E75">
-        <v>181.1200000000001</v>
+        <v>201.76</v>
       </c>
       <c r="F75">
-        <v>1506.72</v>
+        <v>1527.36</v>
       </c>
       <c r="G75">
         <v>175.2</v>
@@ -7431,28 +7431,28 @@
         <v>329.4</v>
       </c>
       <c r="M75">
-        <v>92.361936</v>
+        <v>93.627168</v>
       </c>
       <c r="N75">
-        <v>237.038064</v>
+        <v>235.772832</v>
       </c>
       <c r="O75">
-        <v>59.25951599999999</v>
+        <v>58.943208</v>
       </c>
       <c r="P75">
-        <v>177.778548</v>
+        <v>176.829624</v>
       </c>
       <c r="Q75">
-        <v>248.878548</v>
+        <v>247.929624</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1449326119407162</v>
+        <v>0.1484305869562673</v>
       </c>
       <c r="T75">
-        <v>1.98698036639466</v>
+        <v>2.05709258821522</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.566404238213456</v>
+        <v>3.518209586345707</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0726134526086295</v>
+        <v>0.0741083499932656</v>
       </c>
       <c r="C76">
-        <v>638.9270898527013</v>
+        <v>513.1424634823343</v>
       </c>
       <c r="D76">
-        <v>1991.087089852701</v>
+        <v>1885.942463482334</v>
       </c>
       <c r="E76">
-        <v>201.76</v>
+        <v>222.4000000000001</v>
       </c>
       <c r="F76">
-        <v>1527.36</v>
+        <v>1548</v>
       </c>
       <c r="G76">
         <v>175.2</v>
@@ -7513,45 +7513,45 @@
         <v>329.4</v>
       </c>
       <c r="M76">
-        <v>93.627168</v>
+        <v>99.22680000000001</v>
       </c>
       <c r="N76">
-        <v>235.772832</v>
+        <v>230.1732</v>
       </c>
       <c r="O76">
-        <v>58.943208</v>
+        <v>57.54329999999999</v>
       </c>
       <c r="P76">
-        <v>176.829624</v>
+        <v>172.6299</v>
       </c>
       <c r="Q76">
-        <v>247.929624</v>
+        <v>243.7299</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1484305869562673</v>
+        <v>0.1522083999730624</v>
       </c>
       <c r="T76">
-        <v>2.05709258821522</v>
+        <v>2.132813787781424</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.518209586345707</v>
+        <v>3.319667670427747</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0741083499932656</v>
+        <v>0.07404924737790171</v>
       </c>
       <c r="C77">
-        <v>513.1424634823343</v>
+        <v>496.4482015944516</v>
       </c>
       <c r="D77">
-        <v>1885.942463482334</v>
+        <v>1889.888201594452</v>
       </c>
       <c r="E77">
-        <v>222.4000000000001</v>
+        <v>243.0400000000002</v>
       </c>
       <c r="F77">
-        <v>1548</v>
+        <v>1568.64</v>
       </c>
       <c r="G77">
         <v>175.2</v>
@@ -7595,28 +7595,28 @@
         <v>329.4</v>
       </c>
       <c r="M77">
-        <v>99.22680000000001</v>
+        <v>100.549824</v>
       </c>
       <c r="N77">
-        <v>230.1732</v>
+        <v>228.850176</v>
       </c>
       <c r="O77">
-        <v>57.54329999999999</v>
+        <v>57.21254399999999</v>
       </c>
       <c r="P77">
-        <v>172.6299</v>
+        <v>171.637632</v>
       </c>
       <c r="Q77">
-        <v>243.7299</v>
+        <v>242.737632</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1522083999730624</v>
+        <v>0.1563010307412571</v>
       </c>
       <c r="T77">
-        <v>2.132813787781424</v>
+        <v>2.214845087311479</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.319667670427747</v>
+        <v>3.275987832658961</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07404924737790171</v>
+        <v>0.07399014476253782</v>
       </c>
       <c r="C78">
-        <v>496.4482015944516</v>
+        <v>479.7704847398734</v>
       </c>
       <c r="D78">
-        <v>1889.888201594452</v>
+        <v>1893.850484739873</v>
       </c>
       <c r="E78">
-        <v>243.0400000000002</v>
+        <v>263.6800000000001</v>
       </c>
       <c r="F78">
-        <v>1568.64</v>
+        <v>1589.28</v>
       </c>
       <c r="G78">
         <v>175.2</v>
@@ -7677,28 +7677,28 @@
         <v>329.4</v>
       </c>
       <c r="M78">
-        <v>100.549824</v>
+        <v>101.872848</v>
       </c>
       <c r="N78">
-        <v>228.850176</v>
+        <v>227.527152</v>
       </c>
       <c r="O78">
-        <v>57.21254399999999</v>
+        <v>56.88178799999999</v>
       </c>
       <c r="P78">
-        <v>171.637632</v>
+        <v>170.645364</v>
       </c>
       <c r="Q78">
-        <v>242.737632</v>
+        <v>241.745364</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1563010307412571</v>
+        <v>0.1607495424458165</v>
       </c>
       <c r="T78">
-        <v>2.214845087311479</v>
+        <v>2.304009543322408</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.275987832658961</v>
+        <v>3.233442536130922</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07399014476253782</v>
+        <v>0.07393104214717391</v>
       </c>
       <c r="C79">
-        <v>479.7704847398734</v>
+        <v>463.1094172007015</v>
       </c>
       <c r="D79">
-        <v>1893.850484739873</v>
+        <v>1897.829417200702</v>
       </c>
       <c r="E79">
-        <v>263.6800000000001</v>
+        <v>284.3200000000002</v>
       </c>
       <c r="F79">
-        <v>1589.28</v>
+        <v>1609.92</v>
       </c>
       <c r="G79">
         <v>175.2</v>
@@ -7759,28 +7759,28 @@
         <v>329.4</v>
       </c>
       <c r="M79">
-        <v>101.872848</v>
+        <v>103.195872</v>
       </c>
       <c r="N79">
-        <v>227.527152</v>
+        <v>226.204128</v>
       </c>
       <c r="O79">
-        <v>56.88178799999999</v>
+        <v>56.55103199999999</v>
       </c>
       <c r="P79">
-        <v>170.645364</v>
+        <v>169.653096</v>
       </c>
       <c r="Q79">
-        <v>241.745364</v>
+        <v>240.753096</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1607495424458165</v>
+        <v>0.165602464305336</v>
       </c>
       <c r="T79">
-        <v>2.304009543322408</v>
+        <v>2.401279858970695</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.233442536130922</v>
+        <v>3.191988144642064</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07393104214717391</v>
+        <v>0.07387193953181004</v>
       </c>
       <c r="C80">
-        <v>463.1094172007015</v>
+        <v>446.4651041372579</v>
       </c>
       <c r="D80">
-        <v>1897.829417200702</v>
+        <v>1901.825104137258</v>
       </c>
       <c r="E80">
-        <v>284.3200000000002</v>
+        <v>304.9600000000003</v>
       </c>
       <c r="F80">
-        <v>1609.92</v>
+        <v>1630.56</v>
       </c>
       <c r="G80">
         <v>175.2</v>
@@ -7841,28 +7841,28 @@
         <v>329.4</v>
       </c>
       <c r="M80">
-        <v>103.195872</v>
+        <v>104.518896</v>
       </c>
       <c r="N80">
-        <v>226.204128</v>
+        <v>224.881104</v>
       </c>
       <c r="O80">
-        <v>56.55103199999999</v>
+        <v>56.22027599999999</v>
       </c>
       <c r="P80">
-        <v>169.653096</v>
+        <v>168.660828</v>
       </c>
       <c r="Q80">
-        <v>240.753096</v>
+        <v>239.760828</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.165602464305336</v>
+        <v>0.1709175691990954</v>
       </c>
       <c r="T80">
-        <v>2.401279858970695</v>
+        <v>2.507814014204532</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.191988144642064</v>
+        <v>3.151583231418747</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07387193953181004</v>
+        <v>0.07381283691644613</v>
       </c>
       <c r="C81">
-        <v>446.4651041372579</v>
+        <v>429.8376515973566</v>
       </c>
       <c r="D81">
-        <v>1901.825104137258</v>
+        <v>1905.837651597357</v>
       </c>
       <c r="E81">
-        <v>304.9600000000003</v>
+        <v>325.6000000000001</v>
       </c>
       <c r="F81">
-        <v>1630.56</v>
+        <v>1651.2</v>
       </c>
       <c r="G81">
         <v>175.2</v>
@@ -7923,28 +7923,28 @@
         <v>329.4</v>
       </c>
       <c r="M81">
-        <v>104.518896</v>
+        <v>105.84192</v>
       </c>
       <c r="N81">
-        <v>224.881104</v>
+        <v>223.55808</v>
       </c>
       <c r="O81">
-        <v>56.22027599999999</v>
+        <v>55.88951999999999</v>
       </c>
       <c r="P81">
-        <v>168.660828</v>
+        <v>167.66856</v>
       </c>
       <c r="Q81">
-        <v>239.760828</v>
+        <v>238.76856</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1709175691990954</v>
+        <v>0.1767641845822306</v>
       </c>
       <c r="T81">
-        <v>2.507814014204532</v>
+        <v>2.625001584961753</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.151583231418747</v>
+        <v>3.112188441026012</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07381283691644613</v>
+        <v>0.07375373430108224</v>
       </c>
       <c r="C82">
-        <v>429.8376515973566</v>
+        <v>413.2271665256721</v>
       </c>
       <c r="D82">
-        <v>1905.837651597357</v>
+        <v>1909.867166525672</v>
       </c>
       <c r="E82">
-        <v>325.6000000000001</v>
+        <v>346.2400000000002</v>
       </c>
       <c r="F82">
-        <v>1651.2</v>
+        <v>1671.84</v>
       </c>
       <c r="G82">
         <v>175.2</v>
@@ -8005,28 +8005,28 @@
         <v>329.4</v>
       </c>
       <c r="M82">
-        <v>105.84192</v>
+        <v>107.164944</v>
       </c>
       <c r="N82">
-        <v>223.55808</v>
+        <v>222.235056</v>
       </c>
       <c r="O82">
-        <v>55.88951999999999</v>
+        <v>55.55876399999999</v>
       </c>
       <c r="P82">
-        <v>167.66856</v>
+        <v>166.676292</v>
       </c>
       <c r="Q82">
-        <v>238.76856</v>
+        <v>237.776292</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1767641845822306</v>
+        <v>0.1832262331635907</v>
       </c>
       <c r="T82">
-        <v>2.625001584961753</v>
+        <v>2.754524689482893</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.112188441026012</v>
+        <v>3.073766361507173</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07375373430108224</v>
+        <v>0.07369463168571834</v>
       </c>
       <c r="C83">
-        <v>413.2271665256721</v>
+        <v>396.6337567732544</v>
       </c>
       <c r="D83">
-        <v>1909.867166525672</v>
+        <v>1913.913756773254</v>
       </c>
       <c r="E83">
-        <v>346.2400000000002</v>
+        <v>366.8800000000001</v>
       </c>
       <c r="F83">
-        <v>1671.84</v>
+        <v>1692.48</v>
       </c>
       <c r="G83">
         <v>175.2</v>
@@ -8087,28 +8087,28 @@
         <v>329.4</v>
       </c>
       <c r="M83">
-        <v>107.164944</v>
+        <v>108.487968</v>
       </c>
       <c r="N83">
-        <v>222.235056</v>
+        <v>220.912032</v>
       </c>
       <c r="O83">
-        <v>55.55876399999999</v>
+        <v>55.22800799999999</v>
       </c>
       <c r="P83">
-        <v>166.676292</v>
+        <v>165.684024</v>
       </c>
       <c r="Q83">
-        <v>237.776292</v>
+        <v>236.784024</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1832262331635907</v>
+        <v>0.1904062871428797</v>
       </c>
       <c r="T83">
-        <v>2.754524689482893</v>
+        <v>2.898439250061936</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.073766361507173</v>
+        <v>3.036281405879036</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07369463168571834</v>
+        <v>0.07849102907035445</v>
       </c>
       <c r="C84">
-        <v>396.6337567732544</v>
+        <v>95.18611019687273</v>
       </c>
       <c r="D84">
-        <v>1913.913756773254</v>
+        <v>1633.106110196873</v>
       </c>
       <c r="E84">
-        <v>366.8800000000001</v>
+        <v>387.5200000000002</v>
       </c>
       <c r="F84">
-        <v>1692.48</v>
+        <v>1713.12</v>
       </c>
       <c r="G84">
         <v>175.2</v>
@@ -8169,45 +8169,45 @@
         <v>329.4</v>
       </c>
       <c r="M84">
-        <v>108.487968</v>
+        <v>123.173328</v>
       </c>
       <c r="N84">
-        <v>220.912032</v>
+        <v>206.226672</v>
       </c>
       <c r="O84">
-        <v>55.22800799999999</v>
+        <v>51.55666799999999</v>
       </c>
       <c r="P84">
-        <v>165.684024</v>
+        <v>154.6700039999999</v>
       </c>
       <c r="Q84">
-        <v>236.784024</v>
+        <v>225.7700039999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1904062871428797</v>
+        <v>0.1984310533550262</v>
       </c>
       <c r="T84">
-        <v>2.898439250061936</v>
+        <v>3.059284935414985</v>
       </c>
       <c r="U84">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.036281405879036</v>
+        <v>2.674280263012784</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07849102907035445</v>
+        <v>0.07849042645499055</v>
       </c>
       <c r="C85">
-        <v>95.18611019687273</v>
+        <v>74.57621487703773</v>
       </c>
       <c r="D85">
-        <v>1633.106110196873</v>
+        <v>1633.136214877038</v>
       </c>
       <c r="E85">
-        <v>387.5200000000002</v>
+        <v>408.1600000000003</v>
       </c>
       <c r="F85">
-        <v>1713.12</v>
+        <v>1733.76</v>
       </c>
       <c r="G85">
         <v>175.2</v>
@@ -8251,28 +8251,28 @@
         <v>329.4</v>
       </c>
       <c r="M85">
-        <v>123.173328</v>
+        <v>124.657344</v>
       </c>
       <c r="N85">
-        <v>206.226672</v>
+        <v>204.742656</v>
       </c>
       <c r="O85">
-        <v>51.55666799999999</v>
+        <v>51.18566399999999</v>
       </c>
       <c r="P85">
-        <v>154.6700039999999</v>
+        <v>153.556992</v>
       </c>
       <c r="Q85">
-        <v>225.7700039999999</v>
+        <v>224.656992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1984310533550262</v>
+        <v>0.207458915343691</v>
       </c>
       <c r="T85">
-        <v>3.059284935414985</v>
+        <v>3.240236331437166</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.674280263012784</v>
+        <v>2.642443593215013</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07849042645499055</v>
+        <v>0.07848982383962666</v>
       </c>
       <c r="C86">
-        <v>74.57621487703796</v>
+        <v>53.96632066712232</v>
       </c>
       <c r="D86">
-        <v>1633.136214877038</v>
+        <v>1633.166320667122</v>
       </c>
       <c r="E86">
-        <v>408.1600000000001</v>
+        <v>428.8</v>
       </c>
       <c r="F86">
-        <v>1733.76</v>
+        <v>1754.4</v>
       </c>
       <c r="G86">
         <v>175.2</v>
@@ -8333,28 +8333,28 @@
         <v>329.4</v>
       </c>
       <c r="M86">
-        <v>124.657344</v>
+        <v>126.14136</v>
       </c>
       <c r="N86">
-        <v>204.742656</v>
+        <v>203.25864</v>
       </c>
       <c r="O86">
-        <v>51.18566399999999</v>
+        <v>50.81465999999999</v>
       </c>
       <c r="P86">
-        <v>153.556992</v>
+        <v>152.44398</v>
       </c>
       <c r="Q86">
-        <v>224.656992</v>
+        <v>223.5439799999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2074589153436909</v>
+        <v>0.2176904922641777</v>
       </c>
       <c r="T86">
-        <v>3.240236331437163</v>
+        <v>3.445314580262301</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.642443593215013</v>
+        <v>2.61135602153013</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07848982383962666</v>
+        <v>0.07848922122426276</v>
       </c>
       <c r="C87">
-        <v>53.96632066712232</v>
+        <v>33.35642756718835</v>
       </c>
       <c r="D87">
-        <v>1633.166320667122</v>
+        <v>1633.196427567188</v>
       </c>
       <c r="E87">
-        <v>428.8</v>
+        <v>449.4400000000001</v>
       </c>
       <c r="F87">
-        <v>1754.4</v>
+        <v>1775.04</v>
       </c>
       <c r="G87">
         <v>175.2</v>
@@ -8415,28 +8415,28 @@
         <v>329.4</v>
       </c>
       <c r="M87">
-        <v>126.14136</v>
+        <v>127.625376</v>
       </c>
       <c r="N87">
-        <v>203.25864</v>
+        <v>201.774624</v>
       </c>
       <c r="O87">
-        <v>50.81465999999999</v>
+        <v>50.44365599999999</v>
       </c>
       <c r="P87">
-        <v>152.44398</v>
+        <v>151.330968</v>
       </c>
       <c r="Q87">
-        <v>223.5439799999999</v>
+        <v>222.430968</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2176904922641777</v>
+        <v>0.2293837230304483</v>
       </c>
       <c r="T87">
-        <v>3.445314580262301</v>
+        <v>3.679689721776743</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.61135602153013</v>
+        <v>2.580991416628617</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07848922122426276</v>
+        <v>0.07848861860889886</v>
       </c>
       <c r="C88">
-        <v>33.35642756718835</v>
+        <v>12.74653557729698</v>
       </c>
       <c r="D88">
-        <v>1633.196427567188</v>
+        <v>1633.226535577297</v>
       </c>
       <c r="E88">
-        <v>449.4400000000001</v>
+        <v>470.0800000000002</v>
       </c>
       <c r="F88">
-        <v>1775.04</v>
+        <v>1795.68</v>
       </c>
       <c r="G88">
         <v>175.2</v>
@@ -8497,28 +8497,28 @@
         <v>329.4</v>
       </c>
       <c r="M88">
-        <v>127.625376</v>
+        <v>129.109392</v>
       </c>
       <c r="N88">
-        <v>201.774624</v>
+        <v>200.290608</v>
       </c>
       <c r="O88">
-        <v>50.44365599999999</v>
+        <v>50.07265199999999</v>
       </c>
       <c r="P88">
-        <v>151.330968</v>
+        <v>150.217956</v>
       </c>
       <c r="Q88">
-        <v>222.430968</v>
+        <v>221.317956</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2293837230304483</v>
+        <v>0.2428759123761451</v>
       </c>
       <c r="T88">
-        <v>3.679689721776743</v>
+        <v>3.95012257737033</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.580991416628617</v>
+        <v>2.551324848621392</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07848861860889886</v>
+        <v>0.07848801599353497</v>
       </c>
       <c r="C89">
-        <v>12.74653557729698</v>
+        <v>-7.863355302490618</v>
       </c>
       <c r="D89">
-        <v>1633.226535577297</v>
+        <v>1633.256644697509</v>
       </c>
       <c r="E89">
-        <v>470.0800000000002</v>
+        <v>490.72</v>
       </c>
       <c r="F89">
-        <v>1795.68</v>
+        <v>1816.32</v>
       </c>
       <c r="G89">
         <v>175.2</v>
@@ -8579,28 +8579,28 @@
         <v>329.4</v>
       </c>
       <c r="M89">
-        <v>129.109392</v>
+        <v>130.593408</v>
       </c>
       <c r="N89">
-        <v>200.290608</v>
+        <v>198.806592</v>
       </c>
       <c r="O89">
-        <v>50.07265199999999</v>
+        <v>49.70164799999999</v>
       </c>
       <c r="P89">
-        <v>150.217956</v>
+        <v>149.104944</v>
       </c>
       <c r="Q89">
-        <v>221.317956</v>
+        <v>220.204944</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2428759123761451</v>
+        <v>0.2586167999461247</v>
       </c>
       <c r="T89">
-        <v>3.95012257737033</v>
+        <v>4.265627575562848</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.551324848621392</v>
+        <v>2.522332520796149</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07848801599353497</v>
+        <v>0.08109066337817109</v>
       </c>
       <c r="C90">
-        <v>-7.863355302490618</v>
+        <v>-148.9542260954393</v>
       </c>
       <c r="D90">
-        <v>1633.256644697509</v>
+        <v>1512.805773904561</v>
       </c>
       <c r="E90">
-        <v>490.72</v>
+        <v>511.3600000000001</v>
       </c>
       <c r="F90">
-        <v>1816.32</v>
+        <v>1836.96</v>
       </c>
       <c r="G90">
         <v>175.2</v>
@@ -8661,45 +8661,45 @@
         <v>329.4</v>
       </c>
       <c r="M90">
-        <v>130.593408</v>
+        <v>139.241568</v>
       </c>
       <c r="N90">
-        <v>198.806592</v>
+        <v>190.158432</v>
       </c>
       <c r="O90">
-        <v>49.70164799999999</v>
+        <v>47.53960799999999</v>
       </c>
       <c r="P90">
-        <v>149.104944</v>
+        <v>142.618824</v>
       </c>
       <c r="Q90">
-        <v>220.204944</v>
+        <v>213.718824</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2586167999461247</v>
+        <v>0.2772196670742825</v>
       </c>
       <c r="T90">
-        <v>4.265627575562848</v>
+        <v>4.638497118881279</v>
       </c>
       <c r="U90">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.522332520796149</v>
+        <v>2.365672871480447</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08109066337817109</v>
+        <v>0.08111931076280718</v>
       </c>
       <c r="C91">
-        <v>-148.9542260954393</v>
+        <v>-170.8212582189083</v>
       </c>
       <c r="D91">
-        <v>1512.805773904561</v>
+        <v>1511.578741781092</v>
       </c>
       <c r="E91">
-        <v>511.3600000000001</v>
+        <v>532.0000000000002</v>
       </c>
       <c r="F91">
-        <v>1836.96</v>
+        <v>1857.6</v>
       </c>
       <c r="G91">
         <v>175.2</v>
@@ -8743,28 +8743,28 @@
         <v>329.4</v>
       </c>
       <c r="M91">
-        <v>139.241568</v>
+        <v>140.80608</v>
       </c>
       <c r="N91">
-        <v>190.158432</v>
+        <v>188.59392</v>
       </c>
       <c r="O91">
-        <v>47.53960799999999</v>
+        <v>47.14847999999999</v>
       </c>
       <c r="P91">
-        <v>142.618824</v>
+        <v>141.44544</v>
       </c>
       <c r="Q91">
-        <v>213.718824</v>
+        <v>212.54544</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2772196670742825</v>
+        <v>0.2995431076280719</v>
       </c>
       <c r="T91">
-        <v>4.638497118881279</v>
+        <v>5.085940570863397</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.365672871480447</v>
+        <v>2.339387617352886</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08111931076280718</v>
+        <v>0.0811479581474433</v>
       </c>
       <c r="C92">
-        <v>-170.8212582189083</v>
+        <v>-192.6863014715611</v>
       </c>
       <c r="D92">
-        <v>1511.578741781092</v>
+        <v>1510.353698528439</v>
       </c>
       <c r="E92">
-        <v>532.0000000000002</v>
+        <v>552.6400000000001</v>
       </c>
       <c r="F92">
-        <v>1857.6</v>
+        <v>1878.24</v>
       </c>
       <c r="G92">
         <v>175.2</v>
@@ -8825,28 +8825,28 @@
         <v>329.4</v>
       </c>
       <c r="M92">
-        <v>140.80608</v>
+        <v>142.370592</v>
       </c>
       <c r="N92">
-        <v>188.59392</v>
+        <v>187.029408</v>
       </c>
       <c r="O92">
-        <v>47.14847999999999</v>
+        <v>46.75735199999999</v>
       </c>
       <c r="P92">
-        <v>141.44544</v>
+        <v>140.272056</v>
       </c>
       <c r="Q92">
-        <v>212.54544</v>
+        <v>211.372056</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2995431076280719</v>
+        <v>0.3268273127493699</v>
       </c>
       <c r="T92">
-        <v>5.085940570863397</v>
+        <v>5.632815901063763</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.339387617352886</v>
+        <v>2.31368006111824</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0811479581474433</v>
+        <v>0.08117660553207941</v>
       </c>
       <c r="C93">
-        <v>-192.6863014715611</v>
+        <v>-214.5493606850598</v>
       </c>
       <c r="D93">
-        <v>1510.353698528439</v>
+        <v>1509.13063931494</v>
       </c>
       <c r="E93">
-        <v>552.6400000000001</v>
+        <v>573.2800000000002</v>
       </c>
       <c r="F93">
-        <v>1878.24</v>
+        <v>1898.88</v>
       </c>
       <c r="G93">
         <v>175.2</v>
@@ -8907,28 +8907,28 @@
         <v>329.4</v>
       </c>
       <c r="M93">
-        <v>142.370592</v>
+        <v>143.935104</v>
       </c>
       <c r="N93">
-        <v>187.029408</v>
+        <v>185.464896</v>
       </c>
       <c r="O93">
-        <v>46.75735199999999</v>
+        <v>46.36622399999999</v>
       </c>
       <c r="P93">
-        <v>140.272056</v>
+        <v>139.098672</v>
       </c>
       <c r="Q93">
-        <v>211.372056</v>
+        <v>210.198672</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3268273127493699</v>
+        <v>0.3609325691509926</v>
       </c>
       <c r="T93">
-        <v>5.632815901063763</v>
+        <v>6.316410063814222</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.31368006111824</v>
+        <v>2.288531364801737</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08117660553207941</v>
+        <v>0.08120525291671551</v>
       </c>
       <c r="C94">
-        <v>-214.5493606850598</v>
+        <v>-236.41044067543</v>
       </c>
       <c r="D94">
-        <v>1509.13063931494</v>
+        <v>1507.90955932457</v>
       </c>
       <c r="E94">
-        <v>573.2800000000002</v>
+        <v>593.9200000000003</v>
       </c>
       <c r="F94">
-        <v>1898.88</v>
+        <v>1919.52</v>
       </c>
       <c r="G94">
         <v>175.2</v>
@@ -8989,28 +8989,28 @@
         <v>329.4</v>
       </c>
       <c r="M94">
-        <v>143.935104</v>
+        <v>145.499616</v>
       </c>
       <c r="N94">
-        <v>185.464896</v>
+        <v>183.9003839999999</v>
       </c>
       <c r="O94">
-        <v>46.36622399999999</v>
+        <v>45.97509599999999</v>
       </c>
       <c r="P94">
-        <v>139.098672</v>
+        <v>137.925288</v>
       </c>
       <c r="Q94">
-        <v>210.198672</v>
+        <v>209.025288</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3609325691509926</v>
+        <v>0.4047821845245074</v>
       </c>
       <c r="T94">
-        <v>6.316410063814222</v>
+        <v>7.195316844493382</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.288531364801737</v>
+        <v>2.263923500664084</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08120525291671551</v>
+        <v>0.08123390030135161</v>
       </c>
       <c r="C95">
-        <v>-236.41044067543</v>
+        <v>-258.2695462431216</v>
       </c>
       <c r="D95">
-        <v>1507.90955932457</v>
+        <v>1506.690453756878</v>
       </c>
       <c r="E95">
-        <v>593.9200000000003</v>
+        <v>614.5600000000002</v>
       </c>
       <c r="F95">
-        <v>1919.52</v>
+        <v>1940.16</v>
       </c>
       <c r="G95">
         <v>175.2</v>
@@ -9071,28 +9071,28 @@
         <v>329.4</v>
       </c>
       <c r="M95">
-        <v>145.499616</v>
+        <v>147.064128</v>
       </c>
       <c r="N95">
-        <v>183.9003839999999</v>
+        <v>182.335872</v>
       </c>
       <c r="O95">
-        <v>45.97509599999999</v>
+        <v>45.58396799999999</v>
       </c>
       <c r="P95">
-        <v>137.925288</v>
+        <v>136.751904</v>
       </c>
       <c r="Q95">
-        <v>209.025288</v>
+        <v>207.851904</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4047821845245074</v>
+        <v>0.4632483383558604</v>
       </c>
       <c r="T95">
-        <v>7.195316844493382</v>
+        <v>8.367192552065594</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.263923500664084</v>
+        <v>2.239839208103827</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08123390030135161</v>
+        <v>0.08126254768598772</v>
       </c>
       <c r="C96">
-        <v>-258.2695462431216</v>
+        <v>-280.1266821730758</v>
       </c>
       <c r="D96">
-        <v>1506.690453756878</v>
+        <v>1505.473317826924</v>
       </c>
       <c r="E96">
-        <v>614.5600000000002</v>
+        <v>635.2000000000003</v>
       </c>
       <c r="F96">
-        <v>1940.16</v>
+        <v>1960.8</v>
       </c>
       <c r="G96">
         <v>175.2</v>
@@ -9153,28 +9153,28 @@
         <v>329.4</v>
       </c>
       <c r="M96">
-        <v>147.064128</v>
+        <v>148.62864</v>
       </c>
       <c r="N96">
-        <v>182.335872</v>
+        <v>180.77136</v>
       </c>
       <c r="O96">
-        <v>45.58396799999999</v>
+        <v>45.19283999999999</v>
       </c>
       <c r="P96">
-        <v>136.751904</v>
+        <v>135.57852</v>
       </c>
       <c r="Q96">
-        <v>207.851904</v>
+        <v>206.67852</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4632483383558604</v>
+        <v>0.545100953719755</v>
       </c>
       <c r="T96">
-        <v>8.367192552065594</v>
+        <v>10.0078185426667</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.239839208103827</v>
+        <v>2.216261953281682</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08126254768598772</v>
+        <v>0.08129119507062382</v>
       </c>
       <c r="C97">
-        <v>-280.1266821730758</v>
+        <v>-301.9818532347815</v>
       </c>
       <c r="D97">
-        <v>1505.473317826924</v>
+        <v>1504.258146765218</v>
       </c>
       <c r="E97">
-        <v>635.2000000000003</v>
+        <v>655.8400000000001</v>
       </c>
       <c r="F97">
-        <v>1960.8</v>
+        <v>1981.44</v>
       </c>
       <c r="G97">
         <v>175.2</v>
@@ -9235,28 +9235,28 @@
         <v>329.4</v>
       </c>
       <c r="M97">
-        <v>148.62864</v>
+        <v>150.193152</v>
       </c>
       <c r="N97">
-        <v>180.77136</v>
+        <v>179.206848</v>
       </c>
       <c r="O97">
-        <v>45.19283999999999</v>
+        <v>44.80171199999999</v>
       </c>
       <c r="P97">
-        <v>135.57852</v>
+        <v>134.405136</v>
       </c>
       <c r="Q97">
-        <v>206.67852</v>
+        <v>205.505136</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.545100953719755</v>
+        <v>0.6678798767655966</v>
       </c>
       <c r="T97">
-        <v>10.0078185426667</v>
+        <v>12.46875752856835</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.216261953281682</v>
+        <v>2.193175891268331</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08129119507062382</v>
+        <v>0.08131984245525993</v>
       </c>
       <c r="C98">
-        <v>-301.9818532347813</v>
+        <v>-323.8350641823429</v>
       </c>
       <c r="D98">
-        <v>1504.258146765218</v>
+        <v>1503.044935817657</v>
       </c>
       <c r="E98">
-        <v>655.8399999999999</v>
+        <v>676.48</v>
       </c>
       <c r="F98">
-        <v>1981.44</v>
+        <v>2002.08</v>
       </c>
       <c r="G98">
         <v>175.2</v>
@@ -9317,28 +9317,28 @@
         <v>329.4</v>
       </c>
       <c r="M98">
-        <v>150.193152</v>
+        <v>151.757664</v>
       </c>
       <c r="N98">
-        <v>179.206848</v>
+        <v>177.642336</v>
       </c>
       <c r="O98">
-        <v>44.80171199999999</v>
+        <v>44.41058399999999</v>
       </c>
       <c r="P98">
-        <v>134.405136</v>
+        <v>133.231752</v>
       </c>
       <c r="Q98">
-        <v>205.505136</v>
+        <v>204.331752</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6678798767655949</v>
+        <v>0.87251141517533</v>
       </c>
       <c r="T98">
-        <v>12.46875752856832</v>
+        <v>16.57032250507105</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.193175891268331</v>
+        <v>2.170565830533606</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08131984245525993</v>
+        <v>0.08134848983989604</v>
       </c>
       <c r="C99">
-        <v>-323.8350641823429</v>
+        <v>-345.6863197545388</v>
       </c>
       <c r="D99">
-        <v>1503.044935817657</v>
+        <v>1501.833680245461</v>
       </c>
       <c r="E99">
-        <v>676.48</v>
+        <v>697.1200000000001</v>
       </c>
       <c r="F99">
-        <v>2002.08</v>
+        <v>2022.72</v>
       </c>
       <c r="G99">
         <v>175.2</v>
@@ -9399,28 +9399,28 @@
         <v>329.4</v>
       </c>
       <c r="M99">
-        <v>151.757664</v>
+        <v>153.322176</v>
       </c>
       <c r="N99">
-        <v>177.642336</v>
+        <v>176.077824</v>
       </c>
       <c r="O99">
-        <v>44.41058399999999</v>
+        <v>44.01945599999999</v>
       </c>
       <c r="P99">
-        <v>133.231752</v>
+        <v>132.058368</v>
       </c>
       <c r="Q99">
-        <v>204.331752</v>
+        <v>203.158368</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.87251141517533</v>
+        <v>1.281774491994801</v>
       </c>
       <c r="T99">
-        <v>16.57032250507105</v>
+        <v>24.77345245807652</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.170565830533606</v>
+        <v>2.148417199609794</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08134848983989604</v>
+        <v>0.08137713722453215</v>
       </c>
       <c r="C100">
-        <v>-345.6863197545388</v>
+        <v>-367.5356246748847</v>
       </c>
       <c r="D100">
-        <v>1501.833680245461</v>
+        <v>1500.624375325115</v>
       </c>
       <c r="E100">
-        <v>697.1200000000001</v>
+        <v>717.76</v>
       </c>
       <c r="F100">
-        <v>2022.72</v>
+        <v>2043.36</v>
       </c>
       <c r="G100">
         <v>175.2</v>
@@ -9481,28 +9481,28 @@
         <v>329.4</v>
       </c>
       <c r="M100">
-        <v>153.322176</v>
+        <v>154.886688</v>
       </c>
       <c r="N100">
-        <v>176.077824</v>
+        <v>174.513312</v>
       </c>
       <c r="O100">
-        <v>44.01945599999999</v>
+        <v>43.628328</v>
       </c>
       <c r="P100">
-        <v>132.058368</v>
+        <v>130.884984</v>
       </c>
       <c r="Q100">
-        <v>203.158368</v>
+        <v>201.984984</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.281774491994801</v>
+        <v>2.509563722453211</v>
       </c>
       <c r="T100">
-        <v>24.77345245807652</v>
+        <v>49.38284231709294</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.148417199609794</v>
+        <v>2.126716015775352</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08137713722453215</v>
-      </c>
-      <c r="C101">
-        <v>-367.5356246748847</v>
-      </c>
-      <c r="D101">
-        <v>1500.624375325115</v>
-      </c>
-      <c r="E101">
-        <v>717.76</v>
-      </c>
-      <c r="F101">
-        <v>2043.36</v>
-      </c>
-      <c r="G101">
-        <v>175.2</v>
-      </c>
-      <c r="H101">
-        <v>738.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>400.4999999999999</v>
-      </c>
-      <c r="K101">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>329.4</v>
-      </c>
-      <c r="M101">
-        <v>154.886688</v>
-      </c>
-      <c r="N101">
-        <v>174.513312</v>
-      </c>
-      <c r="O101">
-        <v>43.628328</v>
-      </c>
-      <c r="P101">
-        <v>130.884984</v>
-      </c>
-      <c r="Q101">
-        <v>201.984984</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.509563722453211</v>
-      </c>
-      <c r="T101">
-        <v>49.38284231709294</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.126716015775352</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
